--- a/wp/wp-9/wp9_labelling_workbook.xlsx
+++ b/wp/wp-9/wp9_labelling_workbook.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,12 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -107,22 +113,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -132,10 +139,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D24"/>
+  <dimension ref="B1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -544,170 +551,177 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>VERSION 2 (10 Oct 2026). Version 1 hid part of the measured data. If you labelled version 1, start again here from blank; do not copy old labels.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>How to work</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the 'Items' sheet (or judge_validation_packet.md, the same 50 items, easier to read). Take ITEM-001.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2. List every claim the remediation makes: versions, package names, migration steps, statements about what a release fixes or breaks.</t>
+          <t>1. Open the 'Items' sheet (or judge_validation_packet.md, the same 50 items, easier to read). Take ITEM-001.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>3. Check each claim ONLY against the item's MEASURED FACTS and SOURCE PASSAGES. Never your own knowledge, the internet, or an AI tool.</t>
+          <t>2. List every claim the remediation makes: versions, package names, migration steps, statements about what a release fixes or breaks.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>4. On the 'Labels' sheet, pick a label in the yellow cell, and write a one-line note for every label that is not 'faithful'.</t>
+          <t>3. Check each claim ONLY against the item's MEASURED DATA (every line of it) and SOURCE PASSAGES. Never your own knowledge, the internet, or an AI tool.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>5. Repeat for all 50 items. Watch the 'Check' column and the 'Progress' sheet.</t>
+          <t>4. On the 'Labels' sheet, pick a label in the yellow cell, and write a one-line note for every label that is not 'faithful'.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>5. Repeat for all 50 items. Watch the 'Check' column and the 'Progress' sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>6. When 'Progress' says READY TO RETURN, save the file and send it back to Spandan. Do not upload it to GitHub.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr"/>
-    </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
+      <c r="B13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Yellow cell</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>you fill this in (Labels sheet, columns C and D only)</t>
+          <t>Legend</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t>Yellow cell</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>you fill this in (Labels sheet, columns C and D only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="6" t="inlineStr">
+        <is>
           <t>Grey row</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>an example of the expected format, not a real item</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Example of a filled row (illustrative, not one of the 50)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
-      <c r="B19" s="7" t="inlineStr">
+    <row r="20" ht="42" customHeight="1">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>ITEM-000</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>minor_unsupported</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Claim 'release 2.1 also speeds up parsing' is not in the facts or passages; the upgrade to 2.1 is supported by the measured fix.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>The three labels</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="8" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>faithful</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Every material claim is stated by, or directly follows from, the measured facts or the passages shown. 'Not enough information to recommend…' when the sources are indeed thin is faithful.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="8" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>minor_unsupported</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>At most one PERIPHERAL claim is unsupported; the core recommendation is supported.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="8" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>major_unsupported</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>A CORE claim (the recommended version, the replacement package, an assertion that something breaks) is not in the facts or passages shown.</t>
         </is>
@@ -716,7 +730,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="C24:D24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -740,928 +754,928 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Package (ecosystem, version)</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Note (required unless faithful)</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>ITEM-001</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>transformers (pypi, 4.39.2)</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n"/>
-      <c r="D2" s="12" t="n"/>
-      <c r="E2" s="11">
+      <c r="C2" s="13" t="n"/>
+      <c r="D2" s="13" t="n"/>
+      <c r="E2" s="12">
         <f>IF(C2="","to do",IF(AND(C2&lt;&gt;"faithful",TRIM(D2)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>ITEM-002</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>numpy (pypi, 1.19.5)</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n"/>
-      <c r="D3" s="12" t="n"/>
-      <c r="E3" s="11">
+      <c r="C3" s="13" t="n"/>
+      <c r="D3" s="13" t="n"/>
+      <c r="E3" s="12">
         <f>IF(C3="","to do",IF(AND(C3&lt;&gt;"faithful",TRIM(D3)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>ITEM-003</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>h11 (pypi, 0.14.0)</t>
         </is>
       </c>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="11">
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="13" t="n"/>
+      <c r="E4" s="12">
         <f>IF(C4="","to do",IF(AND(C4&lt;&gt;"faithful",TRIM(D4)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>ITEM-004</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>flag-icon-css (npm, 3.5.0)</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11">
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="12">
         <f>IF(C5="","to do",IF(AND(C5&lt;&gt;"faithful",TRIM(D5)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>ITEM-005</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>jsoneditor (npm, 9.1.9)</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="11">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="12">
         <f>IF(C6="","to do",IF(AND(C6&lt;&gt;"faithful",TRIM(D6)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>ITEM-006</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>scikit-learn (pypi, 1.0)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="11">
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="12">
         <f>IF(C7="","to do",IF(AND(C7&lt;&gt;"faithful",TRIM(D7)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>ITEM-007</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>@babel/core (npm, 7.9.6)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="11">
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="13" t="n"/>
+      <c r="E8" s="12">
         <f>IF(C8="","to do",IF(AND(C8&lt;&gt;"faithful",TRIM(D8)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>ITEM-008</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>scipy (pypi, 1.9.3)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="11">
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="12">
         <f>IF(C9="","to do",IF(AND(C9&lt;&gt;"faithful",TRIM(D9)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>ITEM-009</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>@babel/traverse (npm, 7.17.9)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11">
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="12">
         <f>IF(C10="","to do",IF(AND(C10&lt;&gt;"faithful",TRIM(D10)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>ITEM-010</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>transformers (pypi, 4.45.2)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11">
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="12">
         <f>IF(C11="","to do",IF(AND(C11&lt;&gt;"faithful",TRIM(D11)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>ITEM-011</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>@nestjs/common (npm, 8.3.1)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11">
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="12">
         <f>IF(C12="","to do",IF(AND(C12&lt;&gt;"faithful",TRIM(D12)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>ITEM-012</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>@clerk/clerk-react (npm, 4.30.3)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11">
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="12">
         <f>IF(C13="","to do",IF(AND(C13&lt;&gt;"faithful",TRIM(D13)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>ITEM-013</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>jsonwebtoken (npm, 8.3.0)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11">
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="13" t="n"/>
+      <c r="E14" s="12">
         <f>IF(C14="","to do",IF(AND(C14&lt;&gt;"faithful",TRIM(D14)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>ITEM-014</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>sqlparse (pypi, 0.4.1)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11">
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="12">
         <f>IF(C15="","to do",IF(AND(C15&lt;&gt;"faithful",TRIM(D15)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>ITEM-015</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>pandas (pypi, 0.23.0)</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="11">
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="12">
         <f>IF(C16="","to do",IF(AND(C16&lt;&gt;"faithful",TRIM(D16)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>ITEM-016</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>pillow (pypi, 5.0.0)</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="11">
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="12">
         <f>IF(C17="","to do",IF(AND(C17&lt;&gt;"faithful",TRIM(D17)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>ITEM-017</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>black (pypi, 18.6b4)</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11">
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="12">
         <f>IF(C18="","to do",IF(AND(C18&lt;&gt;"faithful",TRIM(D18)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>ITEM-018</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>markdown (pypi, 2.6.11)</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11">
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="12">
         <f>IF(C19="","to do",IF(AND(C19&lt;&gt;"faithful",TRIM(D19)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>ITEM-019</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>typed-ast (pypi, 1.1.0)</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11">
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="12">
         <f>IF(C20="","to do",IF(AND(C20&lt;&gt;"faithful",TRIM(D20)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>ITEM-020</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>sqlparse (pypi, 0.4.1)</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="11">
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="12">
         <f>IF(C21="","to do",IF(AND(C21&lt;&gt;"faithful",TRIM(D21)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>ITEM-021</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>@opentelemetry/tracing (npm, 0.21.0)</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="11">
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="13" t="n"/>
+      <c r="E22" s="12">
         <f>IF(C22="","to do",IF(AND(C22&lt;&gt;"faithful",TRIM(D22)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>ITEM-022</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>flask (pypi, 1.0)</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="11">
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="12">
         <f>IF(C23="","to do",IF(AND(C23&lt;&gt;"faithful",TRIM(D23)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>ITEM-023</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>@azure/identity (npm, 1.5.1)</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="11">
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="12">
         <f>IF(C24="","to do",IF(AND(C24&lt;&gt;"faithful",TRIM(D24)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>ITEM-024</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>fastify (npm, 4.10.2)</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="11">
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="13" t="n"/>
+      <c r="E25" s="12">
         <f>IF(C25="","to do",IF(AND(C25&lt;&gt;"faithful",TRIM(D25)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>ITEM-025</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="12" t="inlineStr">
         <is>
           <t>flag-icon-css (npm, 3.5.0)</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="11">
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13" t="n"/>
+      <c r="E26" s="12">
         <f>IF(C26="","to do",IF(AND(C26&lt;&gt;"faithful",TRIM(D26)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>ITEM-026</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>stylelint-config-factorial (npm, 7.1.1)</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="11">
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="13" t="n"/>
+      <c r="E27" s="12">
         <f>IF(C27="","to do",IF(AND(C27&lt;&gt;"faithful",TRIM(D27)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>ITEM-027</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="12" t="inlineStr">
         <is>
           <t>passport (npm, 0.4.1)</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="11">
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="12">
         <f>IF(C28="","to do",IF(AND(C28&lt;&gt;"faithful",TRIM(D28)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>ITEM-028</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>certifi (pypi, 2023.7.22)</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="11">
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13" t="n"/>
+      <c r="E29" s="12">
         <f>IF(C29="","to do",IF(AND(C29&lt;&gt;"faithful",TRIM(D29)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>ITEM-029</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>scipy (pypi, 1.9.3)</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="11">
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="13" t="n"/>
+      <c r="E30" s="12">
         <f>IF(C30="","to do",IF(AND(C30&lt;&gt;"faithful",TRIM(D30)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>ITEM-030</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="12" t="inlineStr">
         <is>
           <t>tornado (pypi, 5.1.1)</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="11">
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13" t="n"/>
+      <c r="E31" s="12">
         <f>IF(C31="","to do",IF(AND(C31&lt;&gt;"faithful",TRIM(D31)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>ITEM-031</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="12" t="inlineStr">
         <is>
           <t>@react-native-community/bob (npm, 0.17.1)</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="11">
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="12">
         <f>IF(C32="","to do",IF(AND(C32&lt;&gt;"faithful",TRIM(D32)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="12" t="inlineStr">
         <is>
           <t>ITEM-032</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="12" t="inlineStr">
         <is>
           <t>node-uuid (npm, 1.4.8)</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="11">
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="13" t="n"/>
+      <c r="E33" s="12">
         <f>IF(C33="","to do",IF(AND(C33&lt;&gt;"faithful",TRIM(D33)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>ITEM-033</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>h11 (pypi, 0.12.0)</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="11">
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="13" t="n"/>
+      <c r="E34" s="12">
         <f>IF(C34="","to do",IF(AND(C34&lt;&gt;"faithful",TRIM(D34)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>ITEM-034</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>@babel/plugin-proposal-private-methods (npm, 7.18.6)</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="11">
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="13" t="n"/>
+      <c r="E35" s="12">
         <f>IF(C35="","to do",IF(AND(C35&lt;&gt;"faithful",TRIM(D35)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>ITEM-035</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>nodemailer (npm, 6.4.16)</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="11">
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="13" t="n"/>
+      <c r="E36" s="12">
         <f>IF(C36="","to do",IF(AND(C36&lt;&gt;"faithful",TRIM(D36)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>ITEM-036</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>werkzeug (pypi, 2.3.8)</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="11">
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="12">
         <f>IF(C37="","to do",IF(AND(C37&lt;&gt;"faithful",TRIM(D37)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>ITEM-037</t>
         </is>
       </c>
-      <c r="B38" s="11" t="inlineStr">
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>flag-icon-css (npm, 3.5.0)</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="11">
+      <c r="C38" s="13" t="n"/>
+      <c r="D38" s="13" t="n"/>
+      <c r="E38" s="12">
         <f>IF(C38="","to do",IF(AND(C38&lt;&gt;"faithful",TRIM(D38)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>ITEM-038</t>
         </is>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>@babel/plugin-proposal-logical-assignment-operators (npm, 7.20.7)</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="11">
+      <c r="C39" s="13" t="n"/>
+      <c r="D39" s="13" t="n"/>
+      <c r="E39" s="12">
         <f>IF(C39="","to do",IF(AND(C39&lt;&gt;"faithful",TRIM(D39)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="12" t="inlineStr">
         <is>
           <t>ITEM-039</t>
         </is>
       </c>
-      <c r="B40" s="11" t="inlineStr">
+      <c r="B40" s="12" t="inlineStr">
         <is>
           <t>daphne (pypi, 2.1.2)</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="11">
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="12">
         <f>IF(C40="","to do",IF(AND(C40&lt;&gt;"faithful",TRIM(D40)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="12" t="inlineStr">
         <is>
           <t>ITEM-040</t>
         </is>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>axios (npm, 0.24.0)</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="11">
+      <c r="C41" s="13" t="n"/>
+      <c r="D41" s="13" t="n"/>
+      <c r="E41" s="12">
         <f>IF(C41="","to do",IF(AND(C41&lt;&gt;"faithful",TRIM(D41)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>ITEM-041</t>
         </is>
       </c>
-      <c r="B42" s="11" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>axios (npm, 1.5.0)</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="11">
+      <c r="C42" s="13" t="n"/>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="12">
         <f>IF(C42="","to do",IF(AND(C42&lt;&gt;"faithful",TRIM(D42)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>ITEM-042</t>
         </is>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>requests (pypi, 2.20.0)</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="11">
+      <c r="C43" s="13" t="n"/>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="12">
         <f>IF(C43="","to do",IF(AND(C43&lt;&gt;"faithful",TRIM(D43)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>ITEM-043</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>@nestjs/core (npm, 8.0.5)</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n"/>
-      <c r="D44" s="12" t="n"/>
-      <c r="E44" s="11">
+      <c r="C44" s="13" t="n"/>
+      <c r="D44" s="13" t="n"/>
+      <c r="E44" s="12">
         <f>IF(C44="","to do",IF(AND(C44&lt;&gt;"faithful",TRIM(D44)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="12" t="inlineStr">
         <is>
           <t>ITEM-044</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="12" t="inlineStr">
         <is>
           <t>@nextui-org/react (npm, 2.2.10)</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="11">
+      <c r="C45" s="13" t="n"/>
+      <c r="D45" s="13" t="n"/>
+      <c r="E45" s="12">
         <f>IF(C45="","to do",IF(AND(C45&lt;&gt;"faithful",TRIM(D45)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>ITEM-045</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B46" s="12" t="inlineStr">
         <is>
           <t>pyyaml (pypi, 3.12)</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n"/>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="11">
+      <c r="C46" s="13" t="n"/>
+      <c r="D46" s="13" t="n"/>
+      <c r="E46" s="12">
         <f>IF(C46="","to do",IF(AND(C46&lt;&gt;"faithful",TRIM(D46)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>ITEM-046</t>
         </is>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="12" t="inlineStr">
         <is>
           <t>scikit-learn (pypi, 1.1.1)</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="11">
+      <c r="C47" s="13" t="n"/>
+      <c r="D47" s="13" t="n"/>
+      <c r="E47" s="12">
         <f>IF(C47="","to do",IF(AND(C47&lt;&gt;"faithful",TRIM(D47)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>ITEM-047</t>
         </is>
       </c>
-      <c r="B48" s="11" t="inlineStr">
+      <c r="B48" s="12" t="inlineStr">
         <is>
           <t>gdown (pypi, 3.13.0)</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="12" t="n"/>
-      <c r="E48" s="11">
+      <c r="C48" s="13" t="n"/>
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="12">
         <f>IF(C48="","to do",IF(AND(C48&lt;&gt;"faithful",TRIM(D48)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>ITEM-048</t>
         </is>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>pyjwt (pypi, 1.6.0)</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="11">
+      <c r="C49" s="13" t="n"/>
+      <c r="D49" s="13" t="n"/>
+      <c r="E49" s="12">
         <f>IF(C49="","to do",IF(AND(C49&lt;&gt;"faithful",TRIM(D49)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>ITEM-049</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B50" s="12" t="inlineStr">
         <is>
           <t>react-navigation-tabs (npm, 2.5.6)</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="11">
+      <c r="C50" s="13" t="n"/>
+      <c r="D50" s="13" t="n"/>
+      <c r="E50" s="12">
         <f>IF(C50="","to do",IF(AND(C50&lt;&gt;"faithful",TRIM(D50)=""),"note needed","ok"))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>ITEM-050</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="12" t="inlineStr">
         <is>
           <t>webpack-dev-middleware (npm, 3.1.3)</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="11">
+      <c r="C51" s="13" t="n"/>
+      <c r="D51" s="13" t="n"/>
+      <c r="E51" s="12">
         <f>IF(C51="","to do",IF(AND(C51&lt;&gt;"faithful",TRIM(D51)=""),"note needed","ok"))</f>
         <v/>
       </c>
@@ -1697,85 +1711,98 @@
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="90" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Ecosystem</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>MEASURED FACTS (count as evidence)</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>MEASURED DATA (all of it counts as evidence)</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>REMEDIATION TO LABEL</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>Passages shown</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>SOURCE PASSAGES the author was shown (count as evidence)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="126.8222222222222" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+    <row r="2" ht="409" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>ITEM-001</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>transformers</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D2" s="13" t="inlineStr">
+      <c r="D2" s="14" t="inlineStr">
         <is>
           <t>4.39.2</t>
         </is>
       </c>
-      <c r="E2" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-5241 (severity critical, fixed in unknown);
-CVE-2024-11394 (severity high, fixed in 4.48.0);
-CVE-2024-11393 (severity high, fixed in 4.48.0);
-CVE-2024-11392 (severity high, fixed in 4.48.0);
-CVE-2024-11393 (severity high, fixed in 4.48.0)</t>
-        </is>
-      </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 4.39.2
+- Declared specifier: ==4.39.2
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 5.19.0
+- Versions behind the latest release: major 1, minor 18, patch 1
+- Days since the package's latest release: 1
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 44
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2026-5241 / PYSEC-2026-2290: severity critical, CVSS 9.6, fixed in unknown
+  - CVE-2024-11394 / GHSA-hxxf-235m-72v3: severity high, CVSS 8.8, fixed in 4.48.0
+  - CVE-2024-11393 / GHSA-wrfc-pvp9-mr9g: severity high, CVSS 8.8, fixed in 4.48.0
+  - CVE-2024-11392 / PYSEC-2024-227: severity high, CVSS 8.8, fixed in 4.48.0
+  - CVE-2024-11393 / PYSEC-2024-228: severity high, CVSS 8.8, fixed in 4.48.0</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
         <is>
           <t>The project is pinned to **transformers==4.39.2**, which is affected by several high‑severity CVEs and one critical CVE. Advisory data shows that versions ≥ 4.48.0 contain fixes for the high‑severity issues, and the newest release is 5.19.0. Because no release notes were retrieved, the exact migration steps are unknown, so you should review the package’s changelog for any breaking changes before upgrading. Updating the dependency to the latest version will address all known vulnerabilities and keep you up‑to‑date.
 | Package | Fix | Target version | Replacement |
@@ -1783,43 +1810,56 @@
 | transformers | upgrade | 5.19.0 |  |</t>
         </is>
       </c>
-      <c r="G2" s="13" t="n">
+      <c r="G2" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="H2" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="409" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>ITEM-002</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
         <is>
           <t>numpy</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="C3" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D3" s="13" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t>1.19.5</t>
         </is>
       </c>
-      <c r="E3" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2021-33430 (severity medium, fixed in 1.21);
-CVE-2021-34141 (severity medium, fixed in 1.22)</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.19.5
+- Declared specifier: ==1.19.5
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 2.5.3
+- Versions behind the latest release: major 1, minor 7, patch 0
+- Days since the package's latest release: 31
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: medium
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2021-33430 / GHSA-6p56-wp2h-9hxr: severity medium, CVSS 5.3, fixed in 1.21
+  - CVE-2021-34141 / GHSA-fpfv-jqm9-f5jm: severity medium, CVSS 5.3, fixed in 1.22</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>The current pinned version 1.19.5 is vulnerable to CVE‑2021‑33430 and CVE‑2021‑34141. The advisory data shows the first issue is fixed in NumPy 1.21 and the second in 1.22, so upgrading to at least 1.22 will resolve both problems. The repository’s README does not describe what changed in those releases or any breaking‑migration steps, so you should review NumPy’s release notes separately. Updating the requirement in *requirements.txt* to `numpy&gt;=1.22` (or pinning to `1.22`) will apply the fix.
 | Package | Fix | Target version | Replacement |
@@ -1827,10 +1867,10 @@
 | numpy | upgrade | 1.22 |  |</t>
         </is>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>[Passage 3719f243dccb from README.md]
 .linuxfoundation.org/project/numpy)
@@ -1927,33 +1967,46 @@
       </c>
     </row>
     <row r="4" ht="409" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>ITEM-003</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>h11</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>0.14.0</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2025-43859 (severity critical, fixed in 0.16.0);
-CVE-2025-43859 (severity critical, fixed in 0.16.0)</t>
-        </is>
-      </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.14.0
+- Declared specifier: ==0.14.0
+- Where that version came from: pinned
+- Manifest: requirements-lock.txt
+- Dependency group: runtime
+- Latest release on the registry: 0.16.0
+- Versions behind the latest release: major 0, minor 2, patch 0
+- Days since the package's latest release: 531
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2025-43859 / GHSA-vqfr-h8mv-ghfj: severity critical, CVSS 9.1, fixed in 0.16.0
+  - CVE-2025-43859 / PYSEC-2026-348: severity critical, CVSS 9.1, fixed in 0.16.0</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>Your project pins h11 at version 0.14.0, which is flagged as **critical** (CVE‑2025‑43859) and has a fix in version 0.16.0. Upgrading the `requirements-lock.txt` entry to `h11==0.16.0` will resolve the vulnerability. h11 is a low‑level HTTP/1.1 toolkit rather than a full client library, so the upgrade does not change its API surface [ b1a30cd2b9c3 ].
 | Package | Fix | Target version | Replacement |
@@ -1961,10 +2014,10 @@
 | h11 | upgrade | 0.16.0 |  |</t>
         </is>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>[Passage b1a30cd2b9c3 from README.rst]
 he
@@ -2055,32 +2108,45 @@
       </c>
     </row>
     <row r="5" ht="409" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>ITEM-004</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>flag-icon-css</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>3.5.0</t>
         </is>
       </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: The project has been renamed to flag-icons</t>
-        </is>
-      </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 3.5.0
+- Declared specifier: 3.5.0
+- Where that version came from: pinned
+- Manifest: package.json
+- Dependency group: runtime
+- Latest release on the registry: 4.1.7
+- Versions behind the latest release: major 1, minor 0, patch 0
+- Days since the package's latest release: 1757
+- Deprecated on the registry: yes
+- Registry deprecation message: The project has been renamed to flag-icons
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>The `flag-icon-css` package is deprecated because it was renamed to **flag-icons**. To keep using the flag icons you should replace `flag-icon-css` with the `flag-icons` package, upgrading to at least version 5.0.0 where the rename was introduced. The migration also requires updating CSS class names from `flag-icon`/`flag-icon-[xx]` to `fi`/`fi-[xx]` as noted in the changelog. After updating the `package.json` and any import paths, run your install command to fetch the new package.
 | Package | Fix | Target version | Replacement |
@@ -2088,10 +2154,10 @@
 | flag-icon-css | replace | 5.0.0 | flag-icons |</t>
         </is>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>[Passage 184943b1248b from CHANGELOG.md]
 # 5.0.0
@@ -2127,33 +2193,46 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="104.1857142857143" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+    <row r="6" ht="339.7333333333333" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>ITEM-005</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>jsoneditor</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>9.1.9</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2021-3822 (severity medium, fixed in 9.5.6)</t>
-        </is>
-      </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 9.1.9
+- Declared specifier: ^9.1.9
+- Where that version came from: lockfile
+- Manifest: web/package.json
+- Dependency group: runtime
+- Latest release on the registry: 10.4.3
+- Versions behind the latest release: major 1, minor 9, patch 1
+- Days since the package's latest release: 189
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: medium
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2021-3822 / GHSA-hhfg-6hfc-rvxm: severity medium, CVSS 5.3, fixed in 9.5.6</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>The project is using **jsoneditor** v9.1.9, which is flagged as vulnerable (CVE‑2021‑3822). The advisory data lists a fixed version of 9.5.6, and a newer release 10.4.3 is available. No documentation or changelog passages were retrieved to confirm the fix details, so the safest step is to upgrade to at least the fixed version. Updating the dependency in *web/package.json* will eliminate the known vulnerability and bring you closer to the latest release.
 | Package | Fix | Target version | Replacement |
@@ -2161,44 +2240,57 @@
 | jsoneditor | upgrade | 9.5.6 |  |</t>
         </is>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="107.1571428571428" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+    <row r="7" ht="409" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>ITEM-006</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>scikit-learn</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2020-28975 (severity high, fixed in 1.0.1);
-CVE-2024-5206 (severity medium, fixed in 1.5.0);
-CVE-2024-5206 (severity medium, fixed in 1.5.0)</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.0
+- Declared specifier: ==1.0
+- Where that version came from: pinned
+- Manifest: docker/requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 1.9.1
+- Versions behind the latest release: major 0, minor 9, patch 2
+- Days since the package's latest release: 27
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 3
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 3
+  - CVE-2020-28975 / GHSA-jxfp-4rvq-9h9m: severity high, CVSS 7.5, fixed in 1.0.1
+  - CVE-2024-5206 / GHSA-jw8x-6495-233v: severity medium, CVSS 5.3, fixed in 1.5.0
+  - CVE-2024-5206 / PYSEC-2024-110: severity medium, CVSS 4.7, fixed in 1.5.0</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>The scan flags **scikit-learn==1.0** as vulnerable, listing three advisories (including a high‑severity CVE‑2020‑28975). No changelog or migration notes were retrieved, so we cannot point to a specific release that addresses these issues. The package’s latest version on PyPI is **1.9.1**, and upgrading to that version will apply all available fixes and improvements. Updating the pinned requirement in *docker/requirements.txt* is therefore the recommended remediation.
 | Package | Fix | Target version | Replacement |
@@ -2206,42 +2298,55 @@
 | scikit-learn | upgrade | 1.9.1 |  |</t>
         </is>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="409" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>ITEM-007</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>@babel/core</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>7.9.6</t>
         </is>
       </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-49356 (severity low, fixed in 8.0.0-rc.6)</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 7.9.6
+- Declared specifier: ^7.8.6
+- Where that version came from: lockfile
+- Manifest: app/package.json
+- Dependency group: development
+- Latest release on the registry: 8.0.7
+- Versions behind the latest release: major 1, minor 20, patch 0
+- Days since the package's latest release: 0
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: low
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2026-49356 / GHSA-4x5r-pxfx-6jf8: severity low, CVSS 3.2, fixed in 8.0.0-rc.6</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>Your project is using @babel/core 7.9.6, which is flagged as vulnerable (CVE‑2026‑49356). The advisory indicates the issue is fixed starting with version 8.0.0‑rc.6, so upgrading to at least that release (or the current latest 8.0.7) will resolve the problem. Moving to Babel 8 is a major version bump and introduces breaking changes such as the removal of `preset‑env`’s `useBuiltIns` [#18079] and the removal of corejs2/legacy files from compat‑data [#17633] 【fdc085acc09a】【ee5d6774d733】. After upgrading, test your build pipeline for any required migration steps.
 | Package | Fix | Target version | Replacement |
@@ -2249,10 +2354,10 @@
 | @babel/core | upgrade | 8.0.0-rc.6 |  |</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>[Passage 124a02a8352c from CHANGELOG.md]
 #### :house: Internal
@@ -2295,32 +2400,45 @@
       </c>
     </row>
     <row r="9" ht="409" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>ITEM-008</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>scipy</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>1.9.3</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2023-25399 (severity unknown, fixed in 1.10.0)</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.9.3
+- Declared specifier: ==1.9.3
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 1.18.1
+- Versions behind the latest release: major 0, minor 9, patch 0
+- Days since the package's latest release: 47
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: unknown
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2023-25399 / PYSEC-2023-102: severity unknown, CVSS not recorded, fixed in 1.10.0</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>The SciPy 1.10.0 release is marked as the fixed version for CVE‑2023‑25399, so upgrading from the current 1.9.3 resolves the vulnerability. Updating the `requirements.txt` entry to `scipy==1.10.0` (or any newer version such as the latest 1.18.1) will apply the fix. The README excerpts do not describe any breaking changes or special migration steps for this release, so you should run your test suite after the upgrade to catch any unexpected issues. If you need a newer version for other reasons, you can safely target the latest available release.
 | Package | Fix | Target version | Replacement |
@@ -2328,10 +2446,10 @@
 | scipy | upgrade | 1.10.0 |  |</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>[Passage c9e5c04a7750 from README.rst]
 org/doc/scipy/dev/conduct/code_of_conduct.html
@@ -2422,32 +2540,45 @@
       </c>
     </row>
     <row r="10" ht="409" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>ITEM-009</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>@babel/traverse</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>7.17.9</t>
         </is>
       </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2023-45133 (severity critical, fixed in 7.23.2)</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 7.17.9
+- Declared specifier: 7.17.9
+- Where that version came from: pinned
+- Manifest: packages/core/package.json
+- Dependency group: development
+- Latest release on the registry: 8.0.7
+- Versions behind the latest release: major 1, minor 12, patch 2
+- Days since the package's latest release: 0
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2023-45133 / GHSA-67hx-6x53-jw92: severity critical, CVSS 9.3, fixed in 7.23.2</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>The advisory CVE‑2023‑45133 flags @babel/traverse 7.17.9 as critical and is fixed in version 7.23.2 according to the advisory data. Upgrading the dependency in *packages/core/package.json* to at least 7.23.2 will resolve the vulnerability. The changelog excerpts do not mention this version or any specific migration steps, but they do note a breaking change introduced in Babel 8 (e.g., removal of record and tuple syntax support) 【a7ee65dccf17】. If you plan to move to the latest major version 8.x, review those breaking changes; otherwise a direct upgrade to 7.23.2 should be safe.
 | Package | Fix | Target version | Replacement |
@@ -2455,10 +2586,10 @@
 | @babel/traverse | upgrade | 7.23.2 |  |</t>
         </is>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>[Passage a7d05a4cd351 from CHANGELOG.md]
 #### :bug: Bug Fix
@@ -2501,36 +2632,49 @@
       </c>
     </row>
     <row r="11" ht="409" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>ITEM-010</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>transformers</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D11" s="13" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>4.45.2</t>
         </is>
       </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-5241 (severity critical, fixed in unknown);
-CVE-2024-11394 (severity high, fixed in 4.48.0);
-CVE-2024-11393 (severity high, fixed in 4.48.0);
-CVE-2024-11392 (severity high, fixed in 4.48.0);
-CVE-2024-11393 (severity high, fixed in 4.48.0)</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 4.45.2
+- Declared specifier: ==4.45.2
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 5.19.0
+- Versions behind the latest release: major 1, minor 12, patch 0
+- Days since the package's latest release: 1
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 44
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2026-5241 / PYSEC-2026-2290: severity critical, CVSS 9.6, fixed in unknown
+  - CVE-2024-11394 / GHSA-hxxf-235m-72v3: severity high, CVSS 8.8, fixed in 4.48.0
+  - CVE-2024-11393 / GHSA-wrfc-pvp9-mr9g: severity high, CVSS 8.8, fixed in 4.48.0
+  - CVE-2024-11392 / PYSEC-2024-227: severity high, CVSS 8.8, fixed in 4.48.0
+  - CVE-2024-11393 / PYSEC-2024-228: severity high, CVSS 8.8, fixed in 4.48.0</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>The advisory list shows that versions 4.48.0 of **transformers** fix several high‑severity CVEs (CVE‑2024‑11394, CVE‑2024‑11393, CVE‑2024‑11392) that affect the current 4.45.2 release. Upgrading to at least 4.48.0 will resolve those vulnerabilities, though a critical CVE (CVE‑2026‑5241) remains unfixed. The repository’s README does not provide release‑specific notes or breaking‑change information for the 4.48.0 update, so you should consult the official changelog for any migration concerns. You can upgrade via pip (e.g., `pip install "transformers==4.48.0"`) or to a newer stable version if desired.
 | Package | Fix | Target version | Replacement |
@@ -2538,10 +2682,10 @@
 | transformers | upgrade | 4.48.0 |  |</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>[Passage edef8e3be7d3 from README.md]
 ## 100 projects using Transformers
@@ -2584,32 +2728,45 @@
       </c>
     </row>
     <row r="12" ht="409" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>ITEM-011</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>@nestjs/common</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D12" s="13" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>8.3.1</t>
         </is>
       </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2024-29409 (severity medium, fixed in 11.0.16)</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 8.3.1
+- Declared specifier: ^8.0.0
+- Where that version came from: lockfile
+- Manifest: api/package.json
+- Dependency group: runtime
+- Latest release on the registry: 12.1.2
+- Versions behind the latest release: major 4, minor 1, patch 0
+- Days since the package's latest release: 7
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: medium
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2024-29409 / GHSA-cj7v-w2c7-cp7c: severity medium, CVSS 5.5, fixed in 11.0.16</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>The project is using **@nestjs/common** v8.3.1, which is flagged as vulnerable (CVE‑2024‑29409). The advisory indicates the issue is fixed in version **11.0.16**. Upgrading the dependency to at least 11.0.16 will resolve the vulnerability; you may also consider moving to the latest 12.1.2 if compatible. The repository’s README does not provide details on breaking changes for this upgrade, so review the official NestJS changelog for any migration notes before updating.
 | Package | Fix | Target version | Replacement |
@@ -2617,10 +2774,10 @@
 | @nestjs/common | upgrade | 11.0.16 |  |</t>
         </is>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>[Passage d16ba275076a from Readme.md]
 ## Issues
@@ -2649,33 +2806,45 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="121.2714285714286" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="13" ht="353.0222222222222" customHeight="1">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>ITEM-012</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>@clerk/clerk-react</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>4.30.3</t>
         </is>
       </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: This package is no longer supported. Please use @clerk/react instead. See the upgrade guide for more info: https://clerk.com/docs/guides/development/upgrading/upgrade-guides/core-3</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 4.30.3
+- Declared specifier: ^4.16.2
+- Where that version came from: lockfile
+- Manifest: package.json
+- Dependency group: runtime
+- Latest release on the registry: 5.61.3
+- Versions behind the latest release: major 1, minor 2, patch 7
+- Deprecated on the registry: yes
+- Registry deprecation message: This package is no longer supported. Please use @clerk/react instead. See the upgrade guide for more info: https://clerk.com/docs/guides/development/upgrading/upgrade-guides/core-3
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>The scan flags **@clerk/clerk-react** as deprecated (deprecation_reason: “This package is no longer supported. Please use @clerk/react instead.”). The package is currently at version 4.30.3 and a newer 5.61.3 release exists, but the deprecation notice indicates the library is not maintained any longer. No retrieved documentation was found to confirm a migration path or that the newer version resolves the deprecation. The safest remediation is to replace **@clerk/clerk-react** with the actively‑supported **@clerk/react** package.
 | Package | Fix | Target version | Replacement |
@@ -2683,44 +2852,57 @@
 | @clerk/clerk-react | replace |  | @clerk/react |</t>
         </is>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="409" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>ITEM-013</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>jsonwebtoken</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>8.3.0</t>
         </is>
       </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2022-23539 (severity high, fixed in 9.0.0);
-CVE-2022-23540 (severity medium, fixed in 9.0.0);
-CVE-2022-23541 (severity medium, fixed in 9.0.0)</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 8.3.0
+- Declared specifier: 8.3.0
+- Where that version came from: lockfile
+- Manifest: services/backend/auth-server/package.json
+- Dependency group: runtime
+- Latest release on the registry: 9.0.3
+- Versions behind the latest release: major 1, minor 2, patch 0
+- Days since the package's latest release: 307
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 3
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 3
+  - CVE-2022-23539 / GHSA-8cf7-32gw-wr33: severity high, CVSS 8.1, fixed in 9.0.0
+  - CVE-2022-23540 / GHSA-qwph-4952-7xr6: severity medium, CVSS 6.4, fixed in 9.0.0
+  - CVE-2022-23541 / GHSA-hjrf-2m68-5959: severity medium, CVSS 5.0, fixed in 9.0.0</t>
+        </is>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>The `jsonwebtoken@8.3.0` version you are using is vulnerable to three CVEs that are fixed in version 9.0.0. Upgrading the dependency in `services/backend/auth-server/package.json` to at least `9.0.0` (the latest 9.0.3) will resolve the security issues. Version 9.0.0 introduces breaking changes, so you should follow the migration guide from v8 to v9 before upgrading.
 | Package | Fix | Target version | Replacement |
@@ -2728,10 +2910,10 @@
 | jsonwebtoken | upgrade | 9.0.0 |  |</t>
         </is>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>[Passage 88dd4568902f from CHANGELOG.md]
 ## 9.0.0 - 2022-12-21
@@ -2765,36 +2947,49 @@
       </c>
     </row>
     <row r="15" ht="409" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>ITEM-014</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>sqlparse</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>0.4.1</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2024-4340 (severity high, fixed in 0.5.0);
-CVE-2021-32839 (severity high, fixed in 0.4.2);
-CVE-2026-59893 (severity high, fixed in 0.6.0);
-CVE-2024-4340 (severity high, fixed in 0.5.0);
-CVE-2026-59893 (severity high, fixed in 0.6.0)</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.4.1
+- Declared specifier: ==0.4.1
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 0.6.0
+- Versions behind the latest release: major 0, minor 2, patch 3
+- Days since the package's latest release: 55
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 17
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2024-4340 / GHSA-2m57-hf25-phgg: severity high, CVSS 7.5, fixed in 0.5.0
+  - CVE-2021-32839 / GHSA-p5w8-wqhj-9hhf: severity high, CVSS 7.5, fixed in 0.4.2
+  - CVE-2026-59893 / GHSA-prg7-hcfm-mfcr: severity high, CVSS 7.5, fixed in 0.6.0
+  - CVE-2024-4340 / PYSEC-2026-1940: severity high, CVSS 7.5, fixed in 0.5.0
+  - CVE-2026-59893 / PYSEC-2026-3698: severity high, CVSS 7.5, fixed in 0.6.0</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>The project is using sqlparse 0.4.1, which is vulnerable to CVE‑2024‑4340. Upgrading to **sqlparse 0.5.0** resolves this denial‑of‑service issue – the release notes state it *"Fixes a potential denial of service attack (DOS) due to recursion error for deeply nested statements"*【3ecd17565546】. The upgrade also drops support for Python 3.5‑3.7 and adds support for Python 3.12, so the environment must run a newer Python version (≥3.8). No breaking API changes are mentioned besides added `encoding` keyword support, so the upgrade should be straightforward after confirming Python compatibility.
 | Package | Fix | Target version | Replacement |
@@ -2802,10 +2997,10 @@
 | sqlparse | upgrade | 0.5.0 |  |</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>[Passage cb6e80cba6b1 from CHANGELOG]
 * Improve Python 2/3 compatibility when using parsestream (issue190,
@@ -2916,33 +3111,46 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="96.94285714285715" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="16" ht="339.1555555555556" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>ITEM-015</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>pandas</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>0.23.0</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2020-13091 (severity unknown, fixed in 1.0.4)</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.23.0
+- Declared specifier: &gt;=0.19.0
+- Where that version came from: lockfile
+- Manifest: Pipfile
+- Dependency group: runtime
+- Latest release on the registry: 3.0.6
+- Versions behind the latest release: major 3, minor 2, patch 4
+- Days since the package's latest release: 20
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: unknown
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2020-13091 / PYSEC-2020-73: severity unknown, CVSS not recorded, fixed in 1.0.4</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>The scan flagged pandas 0.23.0 as vulnerable (CVE‑2020‑13091). The advisory data indicates the issue is fixed starting with version 1.0.4, and a newer release 3.0.6 is available. Upgrade pandas in the Pipfile to at least 1.0.4, preferably the latest 3.0.6, to resolve the vulnerability. No documentation was retrieved to describe any migration steps or breaking changes, so review the pandas release notes after upgrading.
 | Package | Fix | Target version | Replacement |
@@ -2950,46 +3158,59 @@
 | pandas | upgrade | 3.0.6 |  |</t>
         </is>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="409" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>ITEM-016</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>pillow</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>5.0.0</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2021-25289 (severity critical, fixed in 8.1.1);
-CVE-2021-34552 (severity critical, fixed in 8.3.0);
-CVE-2022-22817 (severity critical, fixed in 9.0.1);
-CVE-2020-5312 (severity critical, fixed in 6.2.2);
-CVE-2020-5311 (severity critical, fixed in 6.2.2)</t>
-        </is>
-      </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 5.0.0
+- Declared specifier: ==5.0.0
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 12.3.0
+- Versions behind the latest release: major 7, minor 4, patch 0
+- Days since the package's latest release: 98
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 101
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2021-25289 / GHSA-57h3-9rgr-c24m: severity critical, CVSS 9.8, fixed in 8.1.1
+  - CVE-2021-34552 / GHSA-7534-mm45-c74v: severity critical, CVSS 9.8, fixed in 8.3.0
+  - CVE-2022-22817 / GHSA-8vj2-vxx3-667w: severity critical, CVSS 9.8, fixed in 9.0.1
+  - CVE-2020-5312 / GHSA-p49h-hjvm-jg3h: severity critical, CVSS 9.8, fixed in 6.2.2
+  - CVE-2020-5311 / GHSA-r7rm-8j6h-r933: severity critical, CVSS 9.8, fixed in 6.2.2</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>The project pins Pillow at version 5.0.0, which is affected by several critical CVEs (e.g., CVE‑2021‑25289 fixed in 8.1.1, CVE‑2021‑34552 fixed in 8.3.0, CVE‑2022‑22817 fixed in 9.0.1, and CVE‑2020‑5311/5312 fixed in 6.2.2). All of these fixes are included in newer releases, and the latest available version on PyPI is 12.3.0. Upgrading Pillow in *requirements.txt* to at least the latest version will eliminate the known vulnerabilities. The README links to the official release notes and changelog where the security fixes are documented【6388558f1cc9】. After updating, run your test suite to verify compatibility with the newer Pillow API.
 | Package | Fix | Target version | Replacement |
@@ -2997,10 +3218,10 @@
 | pillow | upgrade | 12.3.0 |  |</t>
         </is>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>[Passage 6388558f1cc9 from README.md]
 ## More information
@@ -3076,35 +3297,48 @@
       </c>
     </row>
     <row r="18" ht="409" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>ITEM-017</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>black</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>18.6b4</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-31900 (severity critical, fixed in 26.3.0);
-CVE-2026-32274 (severity high, fixed in 26.3.1);
-CVE-2024-21503 (severity medium, fixed in 24.3.0);
-CVE-2024-21503 (severity unknown, fixed in 24.3.0)</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 18.6b4
+- Declared specifier: ==18.6b4
+- Where that version came from: pinned
+- Manifest: Pipfile
+- Dependency group: development
+- Latest release on the registry: 26.10.0
+- Versions behind the latest release: major 5, minor 0, patch 0
+- Days since the package's latest release: 3
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 4
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 4
+  - CVE-2026-31900 / PYSEC-2026-2120: severity critical, CVSS 9.8, fixed in 26.3.0
+  - CVE-2026-32274 / PYSEC-2026-2121: severity high, CVSS 7.5, fixed in 26.3.1
+  - CVE-2024-21503 / GHSA-fj7x-q9j7-g6q6: severity medium, CVSS 5.3, fixed in 24.3.0
+  - CVE-2024-21503 / PYSEC-2024-48: severity unknown, CVSS not recorded, fixed in 24.3.0</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>Black 18.6b4 is vulnerable to several CVEs, including CVE‑2024‑21503. The project's changelog states that a milestone release fixes this CVE and strongly encourages upgrading [5989badaffec]. Updating the Black dependency in your Pipfile to a newer, non‑vulnerable version will eliminate the issue. Preferably upgrade to the latest available version.
 | Package | Fix | Target version | Replacement |
@@ -3112,10 +3346,10 @@
 | black | upgrade |  |  |</t>
         </is>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="G18" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>[Passage 12f276e8eb54 from CHANGES.md]
 ### Packaging
@@ -3151,34 +3385,47 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="78.18571428571428" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="19" ht="374.4" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>ITEM-018</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>markdown</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>2.6.11</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2025-69534 (severity medium, fixed in 3.8.1);
-CVE-2025-69534 (severity high, fixed in unknown)</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 2.6.11
+- Declared specifier: ==2.6.11
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 3.11
+- Versions behind the latest release: major 1, minor 0, patch 0
+- Days since the package's latest release: 12
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2025-69534 / GHSA-5wmx-573v-2qwq: severity medium, CVSS 7.5, fixed in 3.8.1
+  - CVE-2025-69534 / PYSEC-2026-89: severity high, CVSS 7.5, fixed in unknown</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>The scan flags **markdown 2.6.11** as vulnerable (high severity). Advisory data shows a fixed version of **3.8.1**, and the package’s latest release is 3.11. No documentation was retrieved, so migration details are unavailable. Upgrade the pinned requirement to at least 3.8.1 (or the newest 3.11) to resolve the issue.
 | Package | Fix | Target version | Replacement |
@@ -3186,44 +3433,57 @@
 | markdown | upgrade | 3.8.1 |  |</t>
         </is>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="96.01428571428572" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="20" ht="409" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>ITEM-019</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>typed-ast</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>1.1.0</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2019-19274 (severity unknown, fixed in 1.3.2);
-CVE-2019-19275 (severity unknown, fixed in 1.3.2)
-Registry deprecation message: Development Status :: 7 - Inactive</t>
-        </is>
-      </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.1.0
+- Declared specifier: ==1.1.0
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 1.5.5
+- Versions behind the latest release: major 0, minor 4, patch 2
+- Days since the package's latest release: 1191
+- Deprecated on the registry: yes
+- Registry deprecation message: Development Status :: 7 - Inactive
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: unknown
+- Why it was flagged: deprecated, vulnerable, stale
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2019-19274 / PYSEC-2019-130: severity unknown, CVSS not recorded, fixed in 1.3.2
+  - CVE-2019-19275 / PYSEC-2019-131: severity unknown, CVSS not recorded, fixed in 1.3.2</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>typed-ast 1.1.0 is deprecated and has two known CVEs. The advisories list version 1.3.2 as the first release that fixes the issues, and a newer 1.5.5 release is available. Because the package’s own changelog was not retrieved, we cannot confirm the exact changes, but upgrading to at least 1.3.2 (or the latest 1.5.5) will resolve the vulnerabilities. Update the pinned requirement in requirements.txt accordingly.
 | Package | Fix | Target version | Replacement |
@@ -3231,46 +3491,59 @@
 | typed-ast | upgrade | 1.3.2 |  |</t>
         </is>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="G20" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="409" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>ITEM-020</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>sqlparse</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>0.4.1</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2024-4340 (severity high, fixed in 0.5.0);
-CVE-2021-32839 (severity high, fixed in 0.4.2);
-CVE-2026-59893 (severity high, fixed in 0.6.0);
-CVE-2024-4340 (severity high, fixed in 0.5.0);
-CVE-2026-59893 (severity high, fixed in 0.6.0)</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.4.1
+- Declared specifier: ==0.4.1
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 0.6.0
+- Versions behind the latest release: major 0, minor 2, patch 3
+- Days since the package's latest release: 55
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 17
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2024-4340 / GHSA-2m57-hf25-phgg: severity high, CVSS 7.5, fixed in 0.5.0
+  - CVE-2021-32839 / GHSA-p5w8-wqhj-9hhf: severity high, CVSS 7.5, fixed in 0.4.2
+  - CVE-2026-59893 / GHSA-prg7-hcfm-mfcr: severity high, CVSS 7.5, fixed in 0.6.0
+  - CVE-2024-4340 / PYSEC-2026-1940: severity high, CVSS 7.5, fixed in 0.5.0
+  - CVE-2026-59893 / PYSEC-2026-3698: severity high, CVSS 7.5, fixed in 0.6.0</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>The project pins **sqlparse==0.4.1**, which is vulnerable to several high‑severity CVEs (CVE‑2024‑4340, CVE‑2021‑32839, CVE‑2026‑59893). The 0.5.0 release introduced a fix for the denial‑of‑service issue (recursion error) that addresses CVE‑2024‑4340 【3ecd17565546】, and later releases (0.6.0) contain the remaining security patches. Upgrading sqlparse to the latest version 0.6.0 (or at least 0.5.0) removes all known vulnerabilities. Update the version constraint in **requirements.txt** accordingly.
 | Package | Fix | Target version | Replacement |
@@ -3278,10 +3551,10 @@
 | sqlparse | upgrade | 0.6.0 |  |</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>[Passage cb6e80cba6b1 from CHANGELOG]
 * Improve Python 2/3 compatibility when using parsestream (issue190,
@@ -3396,32 +3669,45 @@
       </c>
     </row>
     <row r="22" ht="409" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>ITEM-021</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>@opentelemetry/tracing</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>0.21.0</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: Package renamed to @opentelemetry/sdk-trace-base</t>
-        </is>
-      </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.21.0
+- Declared specifier: ^0.21.0
+- Where that version came from: lockfile
+- Manifest: web-app-teams/package.json
+- Dependency group: runtime
+- Latest release on the registry: 0.24.0
+- Versions behind the latest release: major 0, minor 3, patch 0
+- Days since the package's latest release: 1897
+- Deprecated on the registry: yes
+- Registry deprecation message: Package renamed to @opentelemetry/sdk-trace-base
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>The `@opentelemetry/tracing` package is deprecated and has been renamed to `@opentelemetry/sdk-trace-base` (see the deprecation reason). All tracing APIs, including samplers like `AlwaysOnSampler`, have moved to the new package ["eef3c282ae27"]. Additionally, the `sdk-trace-base` package (and its siblings) are being consolidated into the unified `@opentelemetry/sdk-trace` package, with a full migration guide in the 3.x docs ["075af08b2a8e","5b42f1588c8d"]. To keep your project up‑to‑date, replace imports of `@opentelemetry/tracing` with either `@opentelemetry/sdk-trace-base` now, or consider moving directly to `@opentelemetry/sdk-trace` for the longer‑term path.
 | Package | Fix | Target version | Replacement |
@@ -3429,10 +3715,10 @@
 | @opentelemetry/tracing | replace |  | @opentelemetry/sdk-trace-base |</t>
         </is>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="G22" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>[Passage 075af08b2a8e from CHANGELOG.md]
 ### :boom: Breaking Changes
@@ -3478,35 +3764,48 @@
       </c>
     </row>
     <row r="23" ht="409" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>ITEM-022</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>flask</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2023-30861 (severity high, fixed in 2.3.2);
-CVE-2026-27205 (severity medium, fixed in 3.1.3);
-CVE-2026-27205 (severity low, fixed in 3.1.3);
-CVE-2023-30861 (severity unknown, fixed in 2.3.2)</t>
-        </is>
-      </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.0
+- Declared specifier: ==1.0
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 3.1.3
+- Versions behind the latest release: major 2, minor 1, patch 4
+- Days since the package's latest release: 230
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 4
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 4
+  - CVE-2023-30861 / GHSA-m2qf-hxjv-5gpq: severity high, CVSS 7.5, fixed in 2.3.2
+  - CVE-2026-27205 / PYSEC-2026-2151: severity medium, CVSS 4.3, fixed in 3.1.3
+  - CVE-2026-27205 / GHSA-68rp-wp8r-4726: severity low, CVSS not recorded, fixed in 3.1.3
+  - CVE-2023-30861 / PYSEC-2023-62: severity unknown, CVSS not recorded, fixed in 2.3.2</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>The current Flask version 1.0 is vulnerable to CVE‑2023‑30861, which is fixed in Flask 2.3.2 according to the advisory data. Upgrading to 2.3.2 (or newer) will eliminate the high‑severity issue. The README excerpts do not describe the security changes or any breaking‑API impacts introduced in 2.3.2, so you should review the Flask changelog and run your test suite after upgrading. Because the fix addresses a high‑severity vulnerability, prioritize the upgrade promptly.
 | Package | Fix | Target version | Replacement |
@@ -3514,10 +3813,10 @@
 | flask | upgrade | 2.3.2 |  |</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="H23" s="15" t="inlineStr">
         <is>
           <t>[Passage 480204f7dfa8 from README.md]
 # Flask
@@ -3554,32 +3853,45 @@
       </c>
     </row>
     <row r="24" ht="409" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>ITEM-023</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>@azure/identity</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>1.5.1</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2024-35255 (severity medium, fixed in 4.2.1)</t>
-        </is>
-      </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.5.1
+- Declared specifier: ^1.3.0
+- Where that version came from: lockfile
+- Manifest: web-app-external/package.json
+- Dependency group: runtime
+- Latest release on the registry: 4.13.3
+- Versions behind the latest release: major 3, minor 0, patch 1
+- Days since the package's latest release: 23
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: medium
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2024-35255 / GHSA-m5vv-6r4h-3vj9: severity medium, CVSS 5.5, fixed in 4.2.1</t>
+        </is>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
         <is>
           <t>The scan reports a medium‑severity vulnerability (CVE‑2024‑35255) in @azure/identity v1.5.1. Upgrading to the latest 4.x release (currently 4.13.3) will move you past the vulnerable range. When upgrading, follow the Azure SDK migration guide for authentication code changes [0a84ee448aa2].
 | Package | Fix | Target version | Replacement |
@@ -3587,10 +3899,10 @@
 | @azure/identity | upgrade | 4.13.3 |  |</t>
         </is>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="G24" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>[Passage 0a84ee448aa2 from README.md]
 ### Management
@@ -3650,37 +3962,50 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="125.3777777777778" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="25" ht="409" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>ITEM-024</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>fastify</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>4.10.2</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-84504 (severity high, fixed in 5.12.2);
-CVE-2026-84428 (severity high, fixed in 5.12.2);
-CVE-2026-84469 (severity high, fixed in 5.12.2);
-CVE-2026-25223 (severity high, fixed in 5.7.2);
-CVE-2026-76169 (severity high, fixed in 5.12.2)</t>
-        </is>
-      </c>
-      <c r="F25" s="14" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 4.10.2
+- Declared specifier: 4.10.2
+- Where that version came from: pinned
+- Manifest: apps/server/package.json
+- Dependency group: runtime
+- Latest release on the registry: 5.12.5
+- Versions behind the latest release: major 1, minor 19, patch 0
+- Days since the package's latest release: 21
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 9
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2026-84504 / GHSA-667r-xxjv-c9mm: severity high, CVSS 8.1, fixed in 5.12.2
+  - CVE-2026-84428 / GHSA-9q9j-q6p8-xq58: severity high, CVSS 7.5, fixed in 5.12.2
+  - CVE-2026-84469 / GHSA-hwr6-493r-vm6h: severity high, CVSS 7.5, fixed in 5.12.2
+  - CVE-2026-25223 / GHSA-jx2c-rxcm-jvmq: severity high, CVSS 7.5, fixed in 5.7.2
+  - CVE-2026-76169 / GHSA-p68q-wchp-6fh7: severity high, CVSS 7.5, fixed in 5.12.2</t>
+        </is>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>The project is using **fastify 4.10.2**, which is vulnerable to several high‑severity CVEs. All listed advisories are fixed in fastify 5.12.2 (one CVE is fixed in 5.7.2), so upgrading to the latest 5.12.5 will resolve the known issues. Because this is a major version bump, you should run your test suite after the upgrade to catch any breaking changes. No upstream migration notes were retrieved, so verify compatibility manually.
 | Package | Fix | Target version | Replacement |
@@ -3688,42 +4013,55 @@
 | fastify | upgrade | 5.12.5 |  |</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="H25" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="95.64285714285714" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+    <row r="26" ht="340.3111111111111" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>ITEM-025</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>flag-icon-css</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D26" s="14" t="inlineStr">
         <is>
           <t>3.5.0</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: The project has been renamed to flag-icons</t>
-        </is>
-      </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 3.5.0
+- Declared specifier: 3.5.0
+- Where that version came from: pinned
+- Manifest: package.json
+- Dependency group: runtime
+- Latest release on the registry: 4.1.7
+- Versions behind the latest release: major 1, minor 0, patch 0
+- Days since the package's latest release: 1757
+- Deprecated on the registry: yes
+- Registry deprecation message: The project has been renamed to flag-icons
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
         <is>
           <t>The scan reports that **flag-icon-css** is deprecated. The registry data shows a newer version 4.1.7 is available, which may include fixes and the continuation of the project. Upgrading to this version is the primary remediation step. Because no documentation was retrieved, details about a rename or migration path are not available, so you should review the upstream repository for any additional guidance.
 | Package | Fix | Target version | Replacement |
@@ -3731,42 +4069,55 @@
 | flag-icon-css | upgrade | 4.1.7 |  |</t>
         </is>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="G26" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="H26" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="89.32857142857142" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="27" ht="349.5555555555555" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>ITEM-026</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>stylelint-config-factorial</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D27" s="13" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>7.1.1</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: DEPRECATED: Please use stylelint-config-suitcss instead.</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 7.1.1
+- Declared specifier: ^7.0.2
+- Where that version came from: range_latest_approx
+- Manifest: package.json
+- Dependency group: development
+- Latest release on the registry: 7.1.1
+- Versions behind the latest release: major 0, minor 0, patch 0
+- Days since the package's latest release: 3522
+- Deprecated on the registry: yes
+- Registry deprecation message: DEPRECATED: Please use stylelint-config-suitcss instead.
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>The scan flags **stylelint-config-factorial** as deprecated and stale, and no documentation was retrieved to describe a migration path or replacement. Because there is no source information confirming a safe upgrade or successor, you should investigate the necessity of this package and consider removing it or switching to an alternative after further research.
 | Package | Fix | Target version | Replacement |
@@ -3774,42 +4125,55 @@
 | stylelint-config-factorial | investigate |  |  |</t>
         </is>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="H27" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="94.15714285714286" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="28" ht="342.0444444444444" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>ITEM-027</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>passport</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D28" s="13" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>0.4.1</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2022-25896 (severity medium, fixed in 0.6.0)</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.4.1
+- Declared specifier: ^0.4.1
+- Where that version came from: lockfile
+- Manifest: api/package.json
+- Dependency group: runtime
+- Latest release on the registry: 0.7.0
+- Versions behind the latest release: major 0, minor 3, patch 0
+- Days since the package's latest release: 1045
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: medium
+- Why it was flagged: vulnerable, stale
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2022-25896 / GHSA-v923-w3x8-wh69: severity medium, CVSS 4.8, fixed in 0.6.0</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
         <is>
           <t>The scan found a medium‑severity vulnerability (CVE‑2022‑25896) in **passport** 0.4.1 that is fixed in version 0.6.0 or later. Your project is still on 0.4.1 and the latest available release is 0.7.0. Because no upstream documentation was retrieved, the exact changes in the fix are not described here. Upgrade the dependency to the latest version (≥ 0.6.0) to resolve the issue and also reduce staleness.
 | Package | Fix | Target version | Replacement |
@@ -3817,43 +4181,56 @@
 | passport | upgrade | 0.7.0 |  |</t>
         </is>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="G28" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="H28" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="97.87142857142857" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="29" ht="383.3555555555556" customHeight="1">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>ITEM-028</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>certifi</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="14" t="inlineStr">
         <is>
           <t>2023.7.22</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2024-39689 (severity high, fixed in 2024.7.4);
-CVE-2024-39689 (severity low, fixed in 2024.7.4)</t>
-        </is>
-      </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 2023.7.22
+- Declared specifier: ==2023.7.22
+- Where that version came from: pinned
+- Manifest: test_requirements.txt
+- Dependency group: development
+- Latest release on the registry: 2026.7.22
+- Versions behind the latest release: major 3, minor 1, patch 0
+- Days since the package's latest release: 77
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2024-39689 / PYSEC-2024-230: severity high, CVSS 7.5, fixed in 2024.7.4
+  - CVE-2024-39689 / GHSA-248v-346w-9cwc: severity low, CVSS not recorded, fixed in 2024.7.4</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>The pinned version `2023.7.22` of **certifi** is flagged as vulnerable (CVE‑2024‑39689). The advisory data lists version `2024.7.4` as the first release that fixes the issue. Upgrading the requirement in `test_requirements.txt` to at least `2024.7.4` will resolve the high‑severity vulnerability. No replacement package is indicated, but you may investigate a temporary mitigation if an upgrade is not immediately possible.
 | Package | Fix | Target version | Replacement |
@@ -3861,42 +4238,55 @@
 | certifi | upgrade | 2024.7.4 |  |</t>
         </is>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="H29" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="409" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>ITEM-029</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="14" t="inlineStr">
         <is>
           <t>scipy</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="14" t="inlineStr">
         <is>
           <t>1.9.3</t>
         </is>
       </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2023-25399 (severity unknown, fixed in 1.10.0)</t>
-        </is>
-      </c>
-      <c r="F30" s="14" t="inlineStr">
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.9.3
+- Declared specifier: ==1.9.3
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 1.18.1
+- Versions behind the latest release: major 0, minor 9, patch 0
+- Days since the package's latest release: 47
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 1
+- Highest advisory severity: unknown
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 1
+  - CVE-2023-25399 / PYSEC-2023-102: severity unknown, CVSS not recorded, fixed in 1.10.0</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
         <is>
           <t>The scan flagged SciPy 1.9.3 as vulnerable (CVE‑2023‑25399). The advisory data shows the issue is fixed starting with SciPy 1.10.0, and a newer 1.18.1 release is available. Upgrade the pinned version in requirements.txt to at least 1.10.0 (or the latest 1.18.1) to resolve the vulnerability. The project’s README does not provide specific migration notes or replacement guidance, so a straightforward version bump is the recommended action.
 | Package | Fix | Target version | Replacement |
@@ -3904,10 +4294,10 @@
 | scipy | upgrade | 1.10.0 |  |</t>
         </is>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="G30" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="H30" s="15" t="inlineStr">
         <is>
           <t>[Passage 5000442d4577 from README.rst]
 uter and display or publish the results, give
@@ -3998,36 +4388,49 @@
       </c>
     </row>
     <row r="31" ht="409" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>ITEM-030</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>tornado</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>5.1.1</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-49853 (severity high, fixed in 6.5.6);
-CVE-2026-49853 (severity high, fixed in 6.5.6);
-CVE-2025-47287 (severity high, fixed in 6.5);
-CVE-2024-52804 (severity high, fixed in 6.4.2);
-CVE-2025-67725 (severity high, fixed in 6.5.3)</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 5.1.1
+- Declared specifier: ==5.1.1
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 6.5.10
+- Versions behind the latest release: major 1, minor 0, patch 0
+- Days since the package's latest release: 22
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 33
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2026-49853 / GHSA-3x9g-8vmp-wqvf: severity high, CVSS 7.7, fixed in 6.5.6
+  - CVE-2026-49853 / PYSEC-2026-3387: severity high, CVSS 7.7, fixed in 6.5.6
+  - CVE-2025-47287 / GHSA-7cx3-6m66-7c5m: severity high, CVSS 7.5, fixed in 6.5
+  - CVE-2024-52804 / GHSA-8w49-h785-mj3c: severity high, CVSS 7.5, fixed in 6.4.2
+  - CVE-2025-67725 / GHSA-c98p-7wgm-6p64: severity high, CVSS 7.5, fixed in 6.5.3</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>Tornado 5.1.1 is flagged as vulnerable; five high‑severity CVEs are listed with fixes in versions 6.4.2, 6.5, 6.5.3 and 6.5.6. The latest release is 6.5.10, which includes all those fixes. Upgrade the dependency to at least 6.5.6 – preferably the newest 6.5.10 – and run your test suite to verify compatibility. The project’s README describes Tornado as a web framework but does not provide migration notes, so no special steps are documented.
 | Package | Fix | Target version | Replacement |
@@ -4035,10 +4438,10 @@
 | tornado | upgrade | 6.5.10 |  |</t>
         </is>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="H31" s="15" t="inlineStr">
         <is>
           <t>[Passage f42209177e51 from README.rst]
 .. image:: docs/tornado.png?raw=true
@@ -4092,32 +4495,45 @@
       </c>
     </row>
     <row r="32" ht="409" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>ITEM-031</t>
         </is>
       </c>
-      <c r="B32" s="13" t="inlineStr">
+      <c r="B32" s="14" t="inlineStr">
         <is>
           <t>@react-native-community/bob</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D32" s="13" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>0.17.1</t>
         </is>
       </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: This package has been renamed to 'react-native-builder-bob'. Please use it instead.</t>
-        </is>
-      </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.17.1
+- Declared specifier: ^0.11.2
+- Where that version came from: range_latest_approx
+- Manifest: package.json
+- Dependency group: development
+- Latest release on the registry: 0.17.1
+- Versions behind the latest release: major 0, minor 0, patch 0
+- Days since the package's latest release: 2120
+- Deprecated on the registry: yes
+- Registry deprecation message: This package has been renamed to 'react-native-builder-bob'. Please use it instead.
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
         <is>
           <t>The `@react-native-community/bob` package is deprecated and has been renamed to **react-native-builder-bob**. Replace the old dependency with the new package and install it from npm. Update any CLI commands to use the new tool, which provides “a set of CLIs to scaffold and build React Native libraries for different targets” 【b09200d81929】. Refer to the documentation at https://oss.callstack.com/react-native-builder-bob/ for migration guidance 【83dbb2a99853】.
 | Package | Fix | Target version | Replacement |
@@ -4125,10 +4541,10 @@
 | @react-native-community/bob | replace |  | react-native-builder-bob |</t>
         </is>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="G32" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="H32" s="15" t="inlineStr">
         <is>
           <t>[Passage 83dbb2a99853 from README.md]
 ## Documentation
@@ -4168,33 +4584,46 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="329.6222222222222" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
+    <row r="33" ht="335.4" customHeight="1">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>ITEM-032</t>
         </is>
       </c>
-      <c r="B33" s="13" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>node-uuid</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D33" s="13" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>1.4.8</t>
         </is>
       </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: Use uuid module instead</t>
-        </is>
-      </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.4.8
+- Declared specifier: 1.4.8
+- Where that version came from: lockfile
+- Manifest: package.json
+- Dependency group: runtime
+- Latest release on the registry: 1.4.8
+- Versions behind the latest release: major 0, minor 0, patch 0
+- Days since the package's latest release: 3486
+- Deprecated on the registry: yes
+- Registry deprecation message: Use uuid module instead
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>The npm package **node-uuid** is marked deprecated and its registry notes suggest using the **uuid** module instead. Since the provided documentation does not detail the migration, you should replace node-uuid with uuid in your package.json and code. Update any `require('node-uuid')` or import statements to `require('uuid')` (or the ES‑module equivalent) and adjust calls to use the uuid API (e.g., `uuid.v4()`). Test your application to ensure the new module works as expected.
 | Package | Fix | Target version | Replacement |
@@ -4202,10 +4631,10 @@
 | node-uuid | replace |  | uuid |</t>
         </is>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="H33" s="15" t="inlineStr">
         <is>
           <t>[Passage 1e4a3a76f4cd from HISTORY.md]
 # 1.3.0
@@ -4227,33 +4656,46 @@
       </c>
     </row>
     <row r="34" ht="409" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>ITEM-033</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="14" t="inlineStr">
         <is>
           <t>h11</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>0.12.0</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2025-43859 (severity critical, fixed in 0.16.0);
-CVE-2025-43859 (severity critical, fixed in 0.16.0)</t>
-        </is>
-      </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.12.0
+- Declared specifier: ==0.12.0
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 0.16.0
+- Versions behind the latest release: major 0, minor 4, patch 0
+- Days since the package's latest release: 531
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2025-43859 / GHSA-vqfr-h8mv-ghfj: severity critical, CVSS 9.1, fixed in 0.16.0
+  - CVE-2025-43859 / PYSEC-2026-348: severity critical, CVSS 9.1, fixed in 0.16.0</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr">
         <is>
           <t>The advisory data shows that the critical vulnerability (CVE‑2025‑43859) is fixed in h11 0.16.0, and your project is currently pinned to 0.12.0. Upgrading the requirement to **0.16.0** will resolve the issue. The README excerpts do not describe what changed in the 0.16.0 release or any breaking‑change considerations, so you should review the project’s changelog or release notes for migration details. After updating the version, run your test suite to ensure compatibility with the newer library.
 | Package | Fix | Target version | Replacement |
@@ -4261,10 +4703,10 @@
 | h11 | upgrade | 0.16.0 |  |</t>
         </is>
       </c>
-      <c r="G34" s="13" t="n">
+      <c r="G34" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="H34" s="15" t="inlineStr">
         <is>
           <t>[Passage b1a30cd2b9c3 from README.rst]
 he
@@ -4355,32 +4797,45 @@
       </c>
     </row>
     <row r="35" ht="409" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>ITEM-034</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>@babel/plugin-proposal-private-methods</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>7.18.6</t>
         </is>
       </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: This proposal has been merged to the ECMAScript standard and thus this plugin is no longer maintained. Please use @babel/plugin-transform-private-methods instead.</t>
-        </is>
-      </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 7.18.6
+- Declared specifier: ^7.18.6
+- Where that version came from: range_latest_approx
+- Manifest: book/10-end/app/package.json
+- Dependency group: development
+- Latest release on the registry: 7.18.6
+- Versions behind the latest release: major 0, minor 0, patch 0
+- Days since the package's latest release: 1563
+- Deprecated on the registry: yes
+- Registry deprecation message: This proposal has been merged to the ECMAScript standard and thus this plugin is no longer maintained. Please use @babel/plugin-transform-private-methods instead.
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
         <is>
           <t>The `@babel/plugin-proposal-private-methods` package is deprecated because its proposal has been merged into the ECMAScript standard. You should replace it with `@babel/plugin-transform-private-methods` in your Babel configuration. The migration mainly consists of swapping the plugin name; no additional options or breaking changes are documented. The replacement plugin is listed among Babel’s plugins in the changelog [0d203f0dd0ca].
 | Package | Fix | Target version | Replacement |
@@ -4388,10 +4843,10 @@
 | @babel/plugin-proposal-private-methods | replace |  | @babel/plugin-transform-private-methods |</t>
         </is>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="H35" s="15" t="inlineStr">
         <is>
           <t>[Passage 0d203f0dd0ca from CHANGELOG.md]
 #### :loudspeaker: Deprecation
@@ -4422,37 +4877,50 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="125.0888888888889" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
+    <row r="36" ht="409" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>ITEM-035</t>
         </is>
       </c>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="B36" s="14" t="inlineStr">
         <is>
           <t>nodemailer</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>6.4.16</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-92596 (severity high, fixed in 9.1.0);
-CVE-2025-14874 (severity high, fixed in 7.0.11);
-CVE-2026-100700 (severity high, fixed in 10.0.6);
-CVE-2026-82659 (severity high, fixed in 9.0.1);
-CVE-2026-82662 (severity high, fixed in 8.0.8)</t>
-        </is>
-      </c>
-      <c r="F36" s="14" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 6.4.16
+- Declared specifier: ^6.3.1
+- Where that version came from: lockfile
+- Manifest: tutorials/backend/hasura/event-trigger/package.json
+- Dependency group: runtime
+- Latest release on the registry: 10.0.16
+- Versions behind the latest release: major 4, minor 6, patch 2
+- Days since the package's latest release: 0
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 16
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2026-92596 / GHSA-2x7j-588g-ccc2: severity high, CVSS 7.5, fixed in 9.1.0
+  - CVE-2025-14874 / GHSA-rcmh-qjqh-p98v: severity high, CVSS 7.5, fixed in 7.0.11
+  - CVE-2026-100700 / GHSA-v53p-9fqp-m79j: severity high, CVSS 7.5, fixed in 10.0.6
+  - CVE-2026-82659 / GHSA-p6gq-j5cr-w38f: severity high, CVSS 7.1, fixed in 9.0.1
+  - CVE-2026-82662 / GHSA-r7g4-qg5f-qqm2: severity high, CVSS 6.5, fixed in 8.0.8</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
         <is>
           <t>The project is using **nodemailer 6.4.16**, which is flagged as vulnerable by several high‑severity CVEs. Each advisory lists a fixed version (e.g., 7.0.11, 8.0.8, 9.0.1, 9.1.0, 10.0.6). Upgrading to the latest available release **10.0.16** satisfies all of those fixed versions and eliminates the reported issues. Update the version constraint in *package.json* and run the install command to apply the new version. This single upgrade addresses the entire advisory set without needing to replace the package.
 | Package | Fix | Target version | Replacement |
@@ -4460,46 +4928,59 @@
 | nodemailer | upgrade | 10.0.16 |  |</t>
         </is>
       </c>
-      <c r="G36" s="13" t="n">
+      <c r="G36" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="H36" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="125.3777777777778" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+    <row r="37" ht="409" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>ITEM-036</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>werkzeug</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>2.3.8</t>
         </is>
       </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2024-34069 (severity high, fixed in 3.0.3);
-CVE-2024-49767 (severity medium, fixed in 3.0.6);
-CVE-2024-34069 (severity high, fixed in 3.0.3);
-CVE-2024-49767 (severity high, fixed in 3.0.6);
-CVE-2026-21860 (severity medium, fixed in 3.1.5)</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 2.3.8
+- Declared specifier: ==2.3.8
+- Where that version came from: pinned
+- Manifest: pyproject.toml
+- Dependency group: runtime
+- Latest release on the registry: 3.1.9
+- Versions behind the latest release: major 1, minor 0, patch 0
+- Days since the package's latest release: 10
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 13
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2024-34069 / GHSA-2g68-c3qc-8985: severity high, CVSS 7.5, fixed in 3.0.3
+  - CVE-2024-49767 / GHSA-q34m-jh98-gwm2: severity medium, CVSS 7.5, fixed in 3.0.6
+  - CVE-2024-34069 / PYSEC-2026-2043: severity high, CVSS 7.5, fixed in 3.0.3
+  - CVE-2024-49767 / PYSEC-2026-3417: severity high, CVSS 7.5, fixed in 3.0.6
+  - CVE-2026-21860 / GHSA-87hc-h4r5-73f7: severity medium, CVSS 5.3, fixed in 3.1.5</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr">
         <is>
           <t>The scan shows that the pinned version **2.3.8** of *werkzeug* is vulnerable to several high‑severity CVEs. The advisory data lists fixed versions 3.0.3, 3.0.6, and 3.1.5, and the latest available release is 3.1.9. Upgrading to the latest version will address all known fixes. No additional documentation was retrieved for this package, so the upgrade path is based solely on the advisory information.
 | Package | Fix | Target version | Replacement |
@@ -4507,42 +4988,55 @@
 | werkzeug | upgrade | 3.1.9 |  |</t>
         </is>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="H37" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="409" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>ITEM-037</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>flag-icon-css</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>3.5.0</t>
         </is>
       </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: The project has been renamed to flag-icons</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 3.5.0
+- Declared specifier: 3.5.0
+- Where that version came from: pinned
+- Manifest: package.json
+- Dependency group: runtime
+- Latest release on the registry: 4.1.7
+- Versions behind the latest release: major 1, minor 0, patch 0
+- Days since the package's latest release: 1757
+- Deprecated on the registry: yes
+- Registry deprecation message: The project has been renamed to flag-icons
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
         <is>
           <t>The `flag-icon-css` package at version 3.5.0 is deprecated and has been renamed to **flag-icons**. The changelog notes that the package name changed from `flag-icon-css` to `flag-icons` and the CSS class prefixes were updated from `flag-icon`/`flag-icon-[xx]` to `fi`/`fi-[xx]` [184943b1248b]. Because the rename occurs starting with version 5.0.0, continuing to use `flag-icon-css` (even at its latest 4.1.7 release) will keep the project on a stale, deprecated name. Replace the dependency with the new `flag-icons` package and update any class names accordingly to stay current and avoid future breakage.
 | Package | Fix | Target version | Replacement |
@@ -4550,10 +5044,10 @@
 | flag-icon-css | replace |  | flag-icons |</t>
         </is>
       </c>
-      <c r="G38" s="13" t="n">
+      <c r="G38" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H38" s="14" t="inlineStr">
+      <c r="H38" s="15" t="inlineStr">
         <is>
           <t>[Passage 184943b1248b from CHANGELOG.md]
 # 5.0.0
@@ -4590,32 +5084,45 @@
       </c>
     </row>
     <row r="39" ht="409" customHeight="1">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>ITEM-038</t>
         </is>
       </c>
-      <c r="B39" s="13" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>@babel/plugin-proposal-logical-assignment-operators</t>
         </is>
       </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>7.20.7</t>
         </is>
       </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: This proposal has been merged to the ECMAScript standard and thus this plugin is no longer maintained. Please use @babel/plugin-transform-logical-assignment-operators instead.</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 7.20.7
+- Declared specifier: 7.20.7
+- Where that version came from: lockfile
+- Manifest: package.json
+- Dependency group: development
+- Latest release on the registry: 7.20.7
+- Versions behind the latest release: major 0, minor 0, patch 0
+- Days since the package's latest release: 1385
+- Deprecated on the registry: yes
+- Registry deprecation message: This proposal has been merged to the ECMAScript standard and thus this plugin is no longer maintained. Please use @babel/plugin-transform-logical-assignment-operators instead.
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>The `@babel/plugin-proposal-logical-assignment-operators` package is deprecated because its proposal has been merged into the ECMAScript standard, and the plugin is no longer maintained. There is no newer version available (latest = 7.20.7), so the safest remediation is to replace it with the maintained transformer plugin. Switch to `@babel/plugin-transform-logical-assignment-operators`, which appears in Babel’s changelog as the successor for handling logical‑assignment operators. Update your Babel configuration and `package.json` accordingly to use the new plugin.
 | Package | Fix | Target version | Replacement |
@@ -4623,10 +5130,10 @@
 | @babel/plugin-proposal-logical-assignment-operators | replace |  | @babel/plugin-transform-logical-assignment-operators |</t>
         </is>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H39" s="14" t="inlineStr">
+      <c r="H39" s="15" t="inlineStr">
         <is>
           <t>[Passage a110106dd02d from CHANGELOG.md]
 #### :boom: Breaking Change
@@ -4653,35 +5160,48 @@
       </c>
     </row>
     <row r="40" ht="409" customHeight="1">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>ITEM-039</t>
         </is>
       </c>
-      <c r="B40" s="13" t="inlineStr">
+      <c r="B40" s="14" t="inlineStr">
         <is>
           <t>daphne</t>
         </is>
       </c>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D40" s="13" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>2.1.2</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-44545 (severity high, fixed in 4.2.2);
-CVE-2026-44545 (severity medium, fixed in 4.2.2);
-CVE-2026-44546 (severity medium, fixed in 4.2.2);
-CVE-2026-44546 (severity low, fixed in 4.2.2)</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 2.1.2
+- Declared specifier: ==2.1.2
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 4.2.3
+- Versions behind the latest release: major 2, minor 4, patch 0
+- Days since the package's latest release: 78
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 4
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 4
+  - CVE-2026-44545 / PYSEC-2026-213: severity high, CVSS 7.5, fixed in 4.2.2
+  - CVE-2026-44545 / GHSA-rrc9-mx66-ffcm: severity medium, CVSS 5.3, fixed in 4.2.2
+  - CVE-2026-44546 / PYSEC-2026-214: severity medium, CVSS 5.3, fixed in 4.2.2
+  - CVE-2026-44546 / GHSA-xh68-hfp5-5x5m: severity low, CVSS 3.7, fixed in 4.2.2</t>
+        </is>
+      </c>
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>The current pinned version 2.1.2 of **daphne** is vulnerable; the security advisories are fixed starting in version **4.2.2** (the latest is 4.2.3). Upgrading the `requirements.txt` entry to at least `daphne==4.2.2` will resolve the CVE‑2026‑44545 and CVE‑2026‑44546 issues. Daphne now requires Python 3.10 or newer, so ensure your runtime meets that requirement [097c6edf9021]. If you use HTTP/2 you may also need the Twisted `tls` and `http2` extras as described in the README [2f12eda0a1c2].
 | Package | Fix | Target version | Replacement |
@@ -4689,10 +5209,10 @@
 | daphne | upgrade | 4.2.2 |  |</t>
         </is>
       </c>
-      <c r="G40" s="13" t="n">
+      <c r="G40" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="14" t="inlineStr">
+      <c r="H40" s="15" t="inlineStr">
         <is>
           <t>[Passage 46de45cda448 from README.rst]
 02,741 INFO     Starting server at ssl:port=8000:privateKey=privkey.pem:certKey=cert.pem, channel layer django_project.asgi:channel_layer.
@@ -4796,37 +5316,50 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="126.2444444444445" customHeight="1">
-      <c r="A41" s="13" t="inlineStr">
+    <row r="41" ht="409" customHeight="1">
+      <c r="A41" s="14" t="inlineStr">
         <is>
           <t>ITEM-040</t>
         </is>
       </c>
-      <c r="B41" s="13" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>axios</t>
         </is>
       </c>
-      <c r="C41" s="13" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D41" s="13" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>0.24.0</t>
         </is>
       </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-44492 (severity high, fixed in 1.16.0);
-CVE-2026-25639 (severity high, fixed in 1.13.5);
-CVE-2026-42039 (severity medium, fixed in 1.15.1);
-CVE-2026-44496 (severity high, fixed in 1.16.0);
-CVE-2026-44486 (severity high, fixed in 1.16.0)</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 0.24.0
+- Declared specifier: ^0.24.0
+- Where that version came from: lockfile
+- Manifest: client/package.json
+- Dependency group: runtime
+- Latest release on the registry: 1.20.0
+- Versions behind the latest release: major 1, minor 10, patch 0
+- Days since the package's latest release: 42
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 23
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2026-44492 / GHSA-pjwm-pj3p-43mv: severity high, CVSS 8.6, fixed in 1.16.0
+  - CVE-2026-25639 / GHSA-43fc-jf86-j433: severity high, CVSS 7.5, fixed in 1.13.5
+  - CVE-2026-42039 / GHSA-62hf-57xw-28j9: severity medium, CVSS 7.5, fixed in 1.15.1
+  - CVE-2026-44496 / GHSA-hfxv-24rg-xrqf: severity high, CVSS 7.5, fixed in 1.16.0
+  - CVE-2026-44486 / GHSA-j5f8-grm9-p9fc: severity high, CVSS 7.5, fixed in 1.16.0</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>The project is using **axios 0.24.0**, which is flagged as vulnerable with several high‑severity CVEs. The advisory data lists fixed versions starting at 1.16.0, and the latest available release is 1.20.0. No documentation was retrieved to confirm migration details, so the safest remediation is to upgrade to the newest version. Upgrading to 1.20.0 will address all listed vulnerabilities and bring the package up‑to‑date.
 | Package | Fix | Target version | Replacement |
@@ -4834,46 +5367,59 @@
 | axios | upgrade | 1.20.0 |  |</t>
         </is>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H41" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="409" customHeight="1">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>ITEM-041</t>
         </is>
       </c>
-      <c r="B42" s="13" t="inlineStr">
+      <c r="B42" s="14" t="inlineStr">
         <is>
           <t>axios</t>
         </is>
       </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>1.5.0</t>
         </is>
       </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-44494 (severity high, fixed in 1.16.0);
-CVE-2026-25639 (severity high, fixed in 1.13.5);
-CVE-2025-58754 (severity high, fixed in 1.12.0);
-CVE-2026-42039 (severity medium, fixed in 1.15.1);
-CVE-2026-44496 (severity high, fixed in 1.16.0)</t>
-        </is>
-      </c>
-      <c r="F42" s="14" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.5.0
+- Declared specifier: ^1.5.0
+- Where that version came from: lockfile
+- Manifest: package.json
+- Dependency group: runtime
+- Latest release on the registry: 1.20.0
+- Versions behind the latest release: major 0, minor 15, patch 1
+- Days since the package's latest release: 42
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 32
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2026-44494 / GHSA-35jp-ww65-95wh: severity high, CVSS 8.7, fixed in 1.16.0
+  - CVE-2026-25639 / GHSA-43fc-jf86-j433: severity high, CVSS 7.5, fixed in 1.13.5
+  - CVE-2025-58754 / GHSA-4hjh-wcwx-xvwj: severity high, CVSS 7.5, fixed in 1.12.0
+  - CVE-2026-42039 / GHSA-62hf-57xw-28j9: severity medium, CVSS 7.5, fixed in 1.15.1
+  - CVE-2026-44496 / GHSA-hfxv-24rg-xrqf: severity high, CVSS 7.5, fixed in 1.16.0</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>Your project is using axios 1.5.0, which is vulnerable. The advisories list fixed versions 1.12.0, 1.13.5, 1.15.1, and 1.16.0, so any version ≥ 1.16.0 resolves all listed CVEs. The changelog entries we have show that 1.13.5 introduced new contributors [a924aa7b2485] and 1.15.1 also added contributors [6e1a222aea01]; later releases 1.14.0 and 1.15.2 are documented [f166c50a1b22, 6806c88a4f1e]. No notes are available for the 1.16.0 release, so you should review the official changelog for potential breaking changes. Upgrading to the latest 1.20.0 (or at least 1.16.0) via your package.json will eliminate the vulnerabilities.
 | Package | Fix | Target version | Replacement |
@@ -4881,10 +5427,10 @@
 | axios | upgrade | 1.20.0 |  |</t>
         </is>
       </c>
-      <c r="G42" s="13" t="n">
+      <c r="G42" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H42" s="15" t="inlineStr">
         <is>
           <t>[Passage a924aa7b2485 from CHANGELOG.md]
 ## 🌟 New Contributors
@@ -4922,36 +5468,49 @@
       </c>
     </row>
     <row r="43" ht="409" customHeight="1">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>ITEM-042</t>
         </is>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>requests</t>
         </is>
       </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>2.20.0</t>
         </is>
       </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2023-32681 (severity medium, fixed in 2.31.0);
-CVE-2024-35195 (severity medium, fixed in 2.32.0);
-CVE-2024-35195 (severity medium, fixed in 2.32.0);
-CVE-2026-25645 (severity medium, fixed in 2.33.0);
-CVE-2024-47081 (severity medium, fixed in 2.32.4)</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="inlineStr">
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 2.20.0
+- Declared specifier: ==2.20.0
+- Where that version came from: pinned
+- Manifest: dev_requirements.txt
+- Dependency group: development
+- Latest release on the registry: 2.34.2
+- Versions behind the latest release: major 0, minor 14, patch 1
+- Days since the package's latest release: 146
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 8
+- Highest advisory severity: medium
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2023-32681 / GHSA-j8r2-6x86-q33q: severity medium, CVSS 6.1, fixed in 2.31.0
+  - CVE-2024-35195 / GHSA-9wx4-h78v-vm56: severity medium, CVSS 5.6, fixed in 2.32.0
+  - CVE-2024-35195 / PYSEC-2026-1873: severity medium, CVSS 5.6, fixed in 2.32.0
+  - CVE-2026-25645 / PYSEC-2026-2275: severity medium, CVSS 5.5, fixed in 2.33.0
+  - CVE-2024-47081 / GHSA-9hjg-9r4m-mvj7: severity medium, CVSS 5.3, fixed in 2.32.4</t>
+        </is>
+      </c>
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>Version 2.31.0 of **requests** adds a security fix that stops forwarding the `Proxy-Authorization` header to destination servers on HTTPS redirects, addressing CVE‑2023‑32681 【cf70c1403035】. The change is described as a fix for proxy‑credential leakage and users are encouraged to upgrade to 2.31.0 or later 【ac038485e0f9】. No breaking API changes are reported for this release, so the upgrade is safe for most codebases. If you use proxy URLs with embedded credentials, you should rotate those credentials after upgrading to ensure any previously leaked tokens are invalidated.
 | Package | Fix | Target version | Replacement |
@@ -4959,10 +5518,10 @@
 | requests | upgrade | 2.31.0 |  |</t>
         </is>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="14" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr">
         <is>
           <t>[Passage 43ae54dca851 from HISTORY.md]
 subclass of `Mapping` is now treated like a
@@ -5077,33 +5636,46 @@
       </c>
     </row>
     <row r="44" ht="409" customHeight="1">
-      <c r="A44" s="13" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>ITEM-043</t>
         </is>
       </c>
-      <c r="B44" s="13" t="inlineStr">
+      <c r="B44" s="14" t="inlineStr">
         <is>
           <t>@nestjs/core</t>
         </is>
       </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D44" s="13" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>8.0.5</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-35515 (severity medium, fixed in 11.1.18);
-CVE-2023-26108 (severity medium, fixed in 9.0.5)</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="inlineStr">
+      <c r="E44" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 8.0.5
+- Declared specifier: ^8.0.5
+- Where that version came from: lockfile
+- Manifest: api/package.json
+- Dependency group: runtime
+- Latest release on the registry: 12.1.2
+- Versions behind the latest release: major 4, minor 4, patch 6
+- Days since the package's latest release: 7
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: medium
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2026-35515 / GHSA-36xv-jgw5-4q75: severity medium, CVSS 6.1, fixed in 11.1.18
+  - CVE-2023-26108 / GHSA-4jpv-8r57-pv7j: severity medium, CVSS 5.3, fixed in 9.0.5</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
         <is>
           <t>The project is using @nestjs/core 8.0.5, which is flagged as vulnerable (CVE‑2023‑26108 and CVE‑2026‑35515). The advisory data indicates the issues are fixed in versions 9.0.5 and 11.1.18 respectively, and the newest release is 12.1.2. Upgrading the dependency to at least 9.0.5 – preferably the latest 12.1.2 – will resolve the known vulnerabilities. The package’s README does not contain specific migration notes or breaking‑change guidance, so you should consult the official Nest changelog for any required code adjustments.
 | Package | Fix | Target version | Replacement |
@@ -5111,10 +5683,10 @@
 | @nestjs/core | upgrade | 12.1.2 |  |</t>
         </is>
       </c>
-      <c r="G44" s="13" t="n">
+      <c r="G44" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H44" s="15" t="inlineStr">
         <is>
           <t>[Passage cdf2a7975896 from Readme.md]
 ## Consulting
@@ -5137,32 +5709,45 @@
       </c>
     </row>
     <row r="45" ht="409" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>ITEM-044</t>
         </is>
       </c>
-      <c r="B45" s="13" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>@nextui-org/react</t>
         </is>
       </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D45" s="13" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>2.2.10</t>
         </is>
       </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: This package has been deprecated. Please use @heroui/react instead.</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="inlineStr">
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 2.2.10
+- Declared specifier: ^2.2.10
+- Where that version came from: lockfile
+- Manifest: frontend/package.json
+- Dependency group: runtime
+- Latest release on the registry: 2.6.11
+- Versions behind the latest release: major 0, minor 4, patch 0
+- Days since the package's latest release: 640
+- Deprecated on the registry: yes
+- Registry deprecation message: This package has been deprecated. Please use @heroui/react instead.
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
         <is>
           <t>The `@nextui-org/react` package is deprecated and the maintainers recommend switching to the new `@heroui/react` library. HeroUI is the rebranded successor of NextUI, and the README lists `@heroui/react` as the full component bundle [21eaae5c289c][9baf941894c4]. Replace the dependency in `frontend/package.json` and install the new package (`npm install @heroui/react`). This migration updates imports to the new namespace and avoids using a deprecated library.
 | Package | Fix | Target version | Replacement |
@@ -5170,10 +5755,10 @@
 | @nextui-org/react | replace |  | @heroui/react |</t>
         </is>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="H45" s="15" t="inlineStr">
         <is>
           <t>[Passage 21eaae5c289c from README.md]
 ## Why HeroUI?
@@ -5210,35 +5795,48 @@
       </c>
     </row>
     <row r="46" ht="409" customHeight="1">
-      <c r="A46" s="13" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>ITEM-045</t>
         </is>
       </c>
-      <c r="B46" s="13" t="inlineStr">
+      <c r="B46" s="14" t="inlineStr">
         <is>
           <t>pyyaml</t>
         </is>
       </c>
-      <c r="C46" s="13" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D46" s="13" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>3.12</t>
         </is>
       </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2020-14343 (severity critical, fixed in 5.4);
-CVE-2017-18342 (severity critical, fixed in 5.1);
-CVE-2017-18342 (severity unknown, fixed in 5.1);
-CVE-2020-14343 (severity unknown, fixed in 5.4)</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 3.12
+- Declared specifier: ==3.12
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 6.0.3
+- Versions behind the latest release: major 2, minor 1, patch 0
+- Days since the package's latest release: 373
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 4
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 4
+  - CVE-2020-14343 / GHSA-8q59-q68h-6hv4: severity critical, CVSS 9.8, fixed in 5.4
+  - CVE-2017-18342 / GHSA-rprw-h62v-c2w7: severity critical, CVSS 9.8, fixed in 5.1
+  - CVE-2017-18342 / PYSEC-2018-49: severity unknown, CVSS not recorded, fixed in 5.1
+  - CVE-2020-14343 / PYSEC-2021-142: severity unknown, CVSS not recorded, fixed in 5.4</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>The scan flags **pyyaml==3.12** as vulnerable (critical CVEs). The README does not mention which release fixes the issues or any migration guidance【01f4a09182a3】. Advisory data indicates that versions 5.1 and 5.4 address the reported CVEs and the latest available version is 6.0.3. Upgrade the entry in requirements.txt to at least 5.4 (preferably the newest 6.0.3) to remediate the vulnerabilities.
 | Package | Fix | Target version | Replacement |
@@ -5246,10 +5844,10 @@
 | pyyaml | upgrade | 6.0.3 |  |</t>
         </is>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="G46" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H46" s="15" t="inlineStr">
         <is>
           <t>[Passage 833adc5f9df1 from README.md]
 ## Further Information
@@ -5302,34 +5900,47 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="92.11428571428571" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+    <row r="47" ht="374.4" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>ITEM-046</t>
         </is>
       </c>
-      <c r="B47" s="13" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>scikit-learn</t>
         </is>
       </c>
-      <c r="C47" s="13" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D47" s="13" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>1.1.1</t>
         </is>
       </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2024-5206 (severity medium, fixed in 1.5.0);
-CVE-2024-5206 (severity medium, fixed in 1.5.0)</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.1.1
+- Declared specifier: ==1.1.1
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 1.9.1
+- Versions behind the latest release: major 0, minor 8, patch 2
+- Days since the package's latest release: 27
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: medium
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2024-5206 / GHSA-jw8x-6495-233v: severity medium, CVSS 5.3, fixed in 1.5.0
+  - CVE-2024-5206 / PYSEC-2024-110: severity medium, CVSS 4.7, fixed in 1.5.0</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
         <is>
           <t>The current pinned version 1.1.1 of **scikit-learn** is vulnerable (CVE‑2024‑5206). Advisory data indicates the issue is fixed starting with version 1.5.0, and a newer 1.9.1 release is available. Upgrade the requirement in `requirements.txt` to at least 1.5.0 (preferably the latest 1.9.1) to resolve the vulnerability. No documentation was retrieved to describe additional migration steps.
 | Package | Fix | Target version | Replacement |
@@ -5337,43 +5948,56 @@
 | scikit-learn | upgrade | 1.5.0 |  |</t>
         </is>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H47" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="96.57142857142857" customHeight="1">
-      <c r="A48" s="13" t="inlineStr">
+    <row r="48" ht="375.8444444444444" customHeight="1">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>ITEM-047</t>
         </is>
       </c>
-      <c r="B48" s="13" t="inlineStr">
+      <c r="B48" s="14" t="inlineStr">
         <is>
           <t>gdown</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>3.13.0</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-40491 (severity high, fixed in 5.2.2);
-CVE-2026-40491 (severity medium, fixed in 5.2.2)</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="inlineStr">
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 3.13.0
+- Declared specifier: ==3.13.0
+- Where that version came from: pinned
+- Manifest: requirements_demo.txt
+- Dependency group: runtime
+- Latest release on the registry: 6.4.1
+- Versions behind the latest release: major 3, minor 2, patch 1
+- Days since the package's latest release: 8
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2026-40491 / PYSEC-2026-2158: severity high, CVSS 7.8, fixed in 5.2.2
+  - CVE-2026-40491 / GHSA-76hw-p97h-883f: severity medium, CVSS 6.5, fixed in 5.2.2</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
         <is>
           <t>The project pins **gdown==3.13.0**, which is reported as vulnerable (CVE‑2026‑40491) with a high severity rating. The scan data indicates the vulnerability is fixed starting in version **5.2.2** and the newest release is **6.4.1**. Upgrade the requirement to at least 5.2.2 (or the latest 6.4.1) to eliminate the issue. No documentation passages were retrieved, so the recommendation is based solely on the scan metadata.
 | Package | Fix | Target version | Replacement |
@@ -5381,46 +6005,59 @@
 | gdown | upgrade | 5.2.2 |  |</t>
         </is>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="G48" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H48" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="409" customHeight="1">
-      <c r="A49" s="13" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>ITEM-048</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>pyjwt</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>pypi</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>1.6.0</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-102268 (severity critical, fixed in 2.14.0);
-CVE-2026-102268 (severity critical, fixed in 2.14.0);
-CVE-2026-32597 (severity high, fixed in 2.12.0);
-CVE-2026-32597 (severity high, fixed in 2.12.0);
-CVE-2026-102267 (severity high, fixed in 2.14.0)</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="inlineStr">
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 1.6.0
+- Declared specifier: ==1.6.0
+- Where that version came from: pinned
+- Manifest: requirements.txt
+- Dependency group: runtime
+- Latest release on the registry: 2.15.1
+- Versions behind the latest release: major 1, minor 1, patch 3
+- Days since the package's latest release: 9
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 19
+- Highest advisory severity: critical
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 5
+  - CVE-2026-102268 / GHSA-ffc3-869f-jxw9: severity critical, CVSS 9.1, fixed in 2.14.0
+  - CVE-2026-102268 / PYSEC-2026-4145: severity critical, CVSS 9.1, fixed in 2.14.0
+  - CVE-2026-32597 / GHSA-752w-5fwx-jx9f: severity high, CVSS 7.5, fixed in 2.12.0
+  - CVE-2026-32597 / PYSEC-2026-120: severity high, CVSS 7.5, fixed in 2.12.0
+  - CVE-2026-102267 / GHSA-9v7f-9g4p-ffgj: severity high, CVSS 7.4, fixed in 2.14.0</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
         <is>
           <t>pyjwt 1.6.0 is affected by several critical and high‑severity vulnerabilities. The advisory data shows that version 2.14.0 (and later) contains fixes for CVE‑2026‑102268 and CVE‑2026‑32597, and the current latest release is 2.15.1. Upgrade the dependency in requirements.txt to at least 2.14.0 (e.g., `pyjwt==2.15.1`). This change does not require code modifications for basic encode/decode usage, but review the release notes for any breaking changes when moving from 1.x to 2.x. After upgrading, re‑run tests to confirm compatibility.
 | Package | Fix | Target version | Replacement |
@@ -5428,10 +6065,10 @@
 | pyjwt | upgrade | 2.14.0 |  |</t>
         </is>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="G49" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H49" s="15" t="inlineStr">
         <is>
           <t>[Passage 439371e9b7ba from README.rst]
 ----------------------------------------------------------------+
@@ -5493,33 +6130,46 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="117.3714285714286" customHeight="1">
-      <c r="A50" s="13" t="inlineStr">
+    <row r="50" ht="390.2888888888889" customHeight="1">
+      <c r="A50" s="14" t="inlineStr">
         <is>
           <t>ITEM-049</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>react-navigation-tabs</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>2.5.6</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>Registry deprecation message: This package is no longer supported. Please use @react-navigation/bottom-tabs instead. See https://reactnavigation.org/docs/bottom-tab-navigator/ for usage guide</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 2.5.6
+- Declared specifier: 2.5.6
+- Where that version came from: pinned
+- Manifest: tutorials/mobile/react-native-apollo/app-boilerplate/package.json
+- Dependency group: runtime
+- Latest release on the registry: 2.11.2
+- Versions behind the latest release: major 0, minor 6, patch 0
+- Days since the package's latest release: 1708
+- Deprecated on the registry: yes
+- Registry deprecation message: This package is no longer supported. Please use @react-navigation/bottom-tabs instead. See https://reactnavigation.org/docs/bottom-tab-navigator/ for usage guide
+- Advisories affecting this version (scanner's count): 0
+- Highest advisory severity: not recorded
+- Why it was flagged: deprecated, stale
+- Advisories in detail (highest CVSS first): none</t>
+        </is>
+      </c>
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>The `react-navigation-tabs` package (v2.5.6) is marked as deprecated and no longer supported. Its deprecation notice advises switching to `@react-navigation/bottom-tabs`. While a newer 2.11.2 release exists, the package remains deprecated, so the safest remediation is to replace it with the recommended bottom‑tabs library. Update your `package.json` to remove `react-navigation-tabs` and add `@react-navigation/bottom-tabs` according to the migration guide linked in the deprecation message.
 | Package | Fix | Target version | Replacement |
@@ -5527,43 +6177,56 @@
 | react-navigation-tabs | replace |  | @react-navigation/bottom-tabs |</t>
         </is>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="G50" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H50" s="15" t="inlineStr">
         <is>
           <t>None. The author was shown no passages for this item; only the measured facts count as evidence.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="409" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>ITEM-050</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>webpack-dev-middleware</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>3.1.3</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>Advisories: CVE-2026-76844 (severity high, fixed in 8.3.0);
-CVE-2024-29180 (severity high, fixed in 7.1.0)</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="inlineStr">
+      <c r="E51" s="14" t="inlineStr">
+        <is>
+          <t>- Version in use: 3.1.3
+- Declared specifier: ^3.1.3
+- Where that version came from: lockfile
+- Manifest: package.json
+- Dependency group: development
+- Latest release on the registry: 8.3.0
+- Versions behind the latest release: major 5, minor 6, patch 0
+- Days since the package's latest release: 34
+- Deprecated on the registry: no
+- Advisories affecting this version (scanner's count): 2
+- Highest advisory severity: high
+- Why it was flagged: vulnerable
+- Advisories in detail (highest CVSS first): 2
+  - CVE-2026-76844 / GHSA-g84c-rxfj-3j2c: severity high, CVSS 7.4, fixed in 8.3.0
+  - CVE-2024-29180 / GHSA-wr3j-pwj9-hqq6: severity high, CVSS 7.4, fixed in 7.1.0</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>The project is using **webpack-dev-middleware 3.1.3**, which is flagged as vulnerable (CVE‑2026‑76844, CVE‑2024‑29180). Both advisories are fixed in version **8.3.0** according to the advisory data, so upgrading to at least that version will resolve the issues. The changelog notes that a release addressed “18 security vulnerabilities”【9937e3929a15】, confirming that security fixes are part of newer releases. Upgrading may involve a major version jump, and the changelog does not provide detailed migration guidance, so review the release notes for potential breaking changes. Apply the upgrade in your package.json to eliminate the high‑severity vulnerabilities.
 | Package | Fix | Target version | Replacement |
@@ -5571,10 +6234,10 @@
 | webpack-dev-middleware | upgrade | 8.3.0 |  |</t>
         </is>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="G51" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="H51" s="14" t="inlineStr">
+      <c r="H51" s="15" t="inlineStr">
         <is>
           <t>[Passage ebcd931ef71a from CHANGELOG.md]
 ### [5.2.1](https://github.com/webpack/webpack-dev-middleware/compare/v5.2.0...v5.2.1) (2021-09-25)
@@ -5621,95 +6284,95 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Items in the packet</t>
         </is>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <f>COUNTA(Labels!$A$2:$A$51)</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Items labelled</t>
         </is>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="12">
         <f>COUNTIF(Labels!$C$2:$C$51,"?*")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  faithful</t>
         </is>
       </c>
-      <c r="B4" s="11">
+      <c r="B4" s="12">
         <f>COUNTIF(Labels!$C$2:$C$51,"faithful")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  minor_unsupported</t>
         </is>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="12">
         <f>COUNTIF(Labels!$C$2:$C$51,"minor_unsupported")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">  major_unsupported</t>
         </is>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="12">
         <f>COUNTIF(Labels!$C$2:$C$51,"major_unsupported")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>Labels that are not one of the three allowed</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="12">
         <f>B3-B4-B5-B6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Non-faithful labels missing a note</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="12">
         <f>SUMPRODUCT((Labels!$C$2:$C$51&lt;&gt;"")*(Labels!$C$2:$C$51&lt;&gt;"faithful")*(LEN(TRIM(Labels!$D$2:$D$51))=0))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="16">
         <f>IF(AND(B3=B2,B7=0,B8=0),"READY TO RETURN","NOT YET")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>These counts are only about your own labels. There is nothing to compare them with: the judge's verdicts are not in this file, by design.</t>
         </is>
